--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.62</v>
+        <v>6.67</v>
       </c>
       <c r="C27" t="inlineStr"/>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33">
@@ -5274,310 +5274,310 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Substance use</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Over the past 2 weeks, did you drink any alcohol?</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>1=Yes 0=No</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="n">
+        <v>89.98</v>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Knowledge/Memory</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>0.178</v>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr"/>
+      <c r="T3" s="6" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Substance use</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Over the past 2 weeks, about how many times did you have 4 or more alcoholic drinks in a row? (1 drink is a can of beer, a glass of wine, a wine cooler, a shot of liquor, or a mixed drink.)</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>1=0 times 2=1 time 3=2 times 4=3 to 5 times 5=6 to 9 times 6=10 or more times 7=Don’t know</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr"/>
+      <c r="P4" s="7" t="inlineStr"/>
+      <c r="Q4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="7" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>Definition adapted from National Institute on Alcohol Abuse and Alcoholism Display if “1=Yes” is selected for “Over the past 2 weeks, did you drink any alcohol?”</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>Definition adapted from National Institute on Alcohol Abuse and Alcoholism Display if “1=Yes” is selected for “Over the past 2 weeks, did you drink any alcohol?”</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>On average, year, how many hours of sleep, on average, do you get on weekend nights?</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Independent Question</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>Dropdown list: 1-8 or more</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>61.45</v>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="n">
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>1=1 2=2 3=3 4=4 5=5 6=6 7=7 8=7+</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>91.33</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>Clarity</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
         <is>
           <t>RANDOM 1 Included if ‘Overall Health’ module not selected</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr">
+      <c r="T5" s="5" t="inlineStr">
         <is>
           <t>RANDOM 1 Included if ‘Overall Health’ module not selected</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="n">
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>On average, how many hours of sleep, on average, do you get on weeknights?</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Independent Question</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>Dropdown list: 1-8 or more</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Numeric</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>1=1 2=2 3=3 4=4 5=5 6=6 7=7 8=7+</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>Clarity</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.189</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr">
         <is>
           <t>RANDOM 1 Included if ‘‘Overall Health’ module not selected</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>RANDOM 1 Included if ‘‘Overall Health’ module not selected</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Substance use</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Over the past 2 weeks, did you drink any alcohol?</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>1=Yes 0=No</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="n">
-        <v>89.98</v>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v>0.178</v>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S5" s="6" t="inlineStr"/>
-      <c r="T5" s="6" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <v>16</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Substance use</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>Over the past 2 weeks, about how many times did you have 4 or more alcoholic drinks in a row? (1 drink is a can of beer, a glass of wine, a wine cooler, a shot of liquor, or a mixed drink.)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>1=0 times 2=1 time 3=2 times 4=3 to 5 times 5=6 to 9 times 6=10 or more times 7=Don’t know</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr"/>
-      <c r="K6" s="7" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr"/>
-      <c r="P6" s="7" t="inlineStr"/>
-      <c r="Q6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="7" t="inlineStr"/>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>Definition adapted from National Institute on Alcohol Abuse and Alcoholism Display if “1=Yes” is selected for “Over the past 2 weeks, did you drink any alcohol?”</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>Definition adapted from National Institute on Alcohol Abuse and Alcoholism Display if “1=Yes” is selected for “Over the past 2 weeks, did you drink any alcohol?”</t>
         </is>
       </c>
     </row>
@@ -8788,7 +8788,7 @@
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>32; 31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -8850,7 +8850,7 @@
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>32; 31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -8912,7 +8912,7 @@
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>32; 31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.41</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="C43" t="inlineStr"/>
     </row>
@@ -1206,7 +1206,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Disability</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -1217,34 +1217,34 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
+          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
+          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Disability</t>
+          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="49">
@@ -7496,17 +7496,17 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>Disability</t>
+          <t>Use of medication</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr"/>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>Are you registered with the office for disability services/ADA office on this campus as having a disability?</t>
+          <t>During the past year, for how long, in total, have you taken the following medication(s)?</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
@@ -7517,228 +7517,210 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>1=Yes 2=No 3=Prefer not to say</t>
+          <t>1=Less than 1 month 2=Between 1 and 2 months 3=2 months or more 4=Did not take</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>84.01000000000001</v>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>What is the source of your current health insurance coverage? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have health insurance through an embassy or sponsoring agency for international students. 7=I have individual health insurance purchased directly from an insurance carrier. 8=I have Medicaid or other governmental insurance. 9=I am uncertain about whether I have health insurance. 10=I have health insurance but am uncertain about where it is from.</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J2" s="5" t="n">
-        <v>38.59</v>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="J3" s="6" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>If any of the disabilities above are selected</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Use of medication</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr"/>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>During the past year, for how long, in total, have you taken the following medication(s)?</t>
-        </is>
-      </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>1=Less than 1 month 2=Between 1 and 2 months 3=2 months or more 4=Did not take</t>
-        </is>
-      </c>
-      <c r="I3" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J3" s="5" t="n">
-        <v>84.01000000000001</v>
-      </c>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O3" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q3" s="5" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="R3" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S3" s="5" t="inlineStr">
-        <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
-      <c r="T3" s="5" t="inlineStr"/>
+      <c r="O3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
+        <is>
+          <t>RANDOM 2</t>
+        </is>
+      </c>
+      <c r="T3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D4" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>What is the source of your current health insurance coverage? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have health insurance through an embassy or sponsoring agency for international students. 7=I have individual health insurance purchased directly from an insurance carrier. 8=I have Medicaid or other governmental insurance. 9=I am uncertain about whether I have health insurance. 10=I have health insurance but am uncertain about where it is from.</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>Do you know if your health insurance plan would provide any coverage for a visit to a mental health professional (such as a psychiatrist, psychologist, clinical social worker, etc.)?</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
+          <t>1=Yes, it definitely would. 2=I think it would but am not sure. 3=I have no idea. 4=I think it would not but am not sure. 5=No, it definitely would not.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J4" s="6" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N4" s="6" t="n">
+      <c r="J4" s="7" t="inlineStr"/>
+      <c r="K4" s="7" t="inlineStr"/>
+      <c r="L4" s="7" t="inlineStr"/>
+      <c r="M4" s="7" t="inlineStr"/>
+      <c r="N4" s="7" t="inlineStr"/>
+      <c r="O4" s="7" t="inlineStr"/>
+      <c r="P4" s="7" t="inlineStr"/>
+      <c r="Q4" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S4" s="6" t="inlineStr">
-        <is>
-          <t>RANDOM 2</t>
-        </is>
-      </c>
-      <c r="T4" s="6" t="inlineStr"/>
+      <c r="R4" s="7" t="inlineStr"/>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
+        <is>
+          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -7750,7 +7732,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Do you know if your health insurance plan would provide any coverage for a visit to a mental health professional (such as a psychiatrist, psychologist, clinical social worker, etc.)?</t>
+          <t>Does your current health insurance plan meet your needs for mental health services?</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -7765,7 +7747,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>1=Yes, it definitely would. 2=I think it would but am not sure. 3=I have no idea. 4=I think it would not but am not sure. 5=No, it definitely would not.</t>
+          <t>1=I have not needed to use my current insurance plan to cover mental health services. 2=Yes, everything I have needed is covered. 3=No, the coverage is inadequate to meet my needs. 4=I’m not sure</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7800,7 +7782,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -7812,7 +7794,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Does your current health insurance plan meet your needs for mental health services?</t>
+          <t>I feel that coverage is inadequate because my plan… (Select all that apply)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -7822,12 +7804,12 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>1=I have not needed to use my current insurance plan to cover mental health services. 2=Yes, everything I have needed is covered. 3=No, the coverage is inadequate to meet my needs. 4=I’m not sure</t>
+          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Other (please specify)</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -7848,165 +7830,165 @@
       <c r="R6" s="7" t="inlineStr"/>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
         </is>
       </c>
       <c r="T6" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>I feel that coverage is inadequate because my plan… (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="B7" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Use of counseling/therapy</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Have you ever received counseling or therapy for mental health concerns?</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>1=No, never 2=Yes, prior to starting at this school 3=Yes, since starting at this school 4=Yes, both of the above (prior to and since starting at this school)</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>75.27</v>
+      </c>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>Sensitivity/Bias</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S7" s="6" t="inlineStr">
+        <is>
+          <t>CCMH Standardized Data Set</t>
+        </is>
+      </c>
+      <c r="T7" s="6" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>Use of counseling/therapy</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>How many total visits or sessions for counseling or therapy have you had in the past 12 months?</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Follow-up Question</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr"/>
-      <c r="K7" s="7" t="inlineStr"/>
-      <c r="L7" s="7" t="inlineStr"/>
-      <c r="M7" s="7" t="inlineStr"/>
-      <c r="N7" s="7" t="inlineStr"/>
-      <c r="O7" s="7" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr"/>
-      <c r="Q7" s="7" t="n">
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>0=0 1=1-3 2=4-6 3=7-9 4=10 or more</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr"/>
+      <c r="K8" s="7" t="inlineStr"/>
+      <c r="L8" s="7" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+      <c r="N8" s="7" t="inlineStr"/>
+      <c r="O8" s="7" t="inlineStr"/>
+      <c r="P8" s="7" t="inlineStr"/>
+      <c r="Q8" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" s="7" t="inlineStr"/>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
-        </is>
-      </c>
-      <c r="T7" s="7" t="inlineStr">
-        <is>
-          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>Use of counseling/therapy</t>
-        </is>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
-        <is>
-          <t>Have you ever received counseling or therapy for mental health concerns?</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>1=No, never 2=Yes, prior to starting at this school 3=Yes, since starting at this school 4=Yes, both of the above (prior to and since starting at this school)</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="n">
-        <v>75.27</v>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>CCMH Standardized Data Set</t>
-        </is>
-      </c>
-      <c r="T8" s="6" t="inlineStr"/>
+      <c r="R8" s="7" t="inlineStr"/>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
+        <is>
+          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -8018,7 +8000,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>How many total visits or sessions for counseling or therapy have you had in the past 12 months?</t>
+          <t>Are you currently receiving counseling or therapy?</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -8028,17 +8010,17 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>0=0 1=1-3 2=4-6 3=7-9 4=10 or more</t>
+          <t>1=Yes 0=No</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Ordinal)</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -8054,12 +8036,12 @@
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
     </row>
@@ -8068,7 +8050,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
@@ -8080,7 +8062,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Are you currently receiving counseling or therapy?</t>
+          <t>From which of the following did you receive counseling or therapy in the past 12 months? (Select all that apply)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -8090,17 +8072,17 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24; 23</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>1=Yes 0=No</t>
+          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Other</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr"/>
@@ -8116,12 +8098,12 @@
       <c r="R10" s="7" t="inlineStr"/>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8112,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
@@ -8142,7 +8124,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>From which of the following did you receive counseling or therapy in the past 12 months? (Select all that apply)</t>
+          <t>Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? [pipe in selected options from the question, “From which of the following places did you receive counseling or therapy?”]</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -8152,17 +8134,17 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>24; 23</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Other</t>
+          <t>1=In-person only 2=Remote/telehealth only (digital video conferencing, text/app chat, etc…) 3=Both in-person and remote</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr"/>
@@ -8178,12 +8160,12 @@
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
     </row>
@@ -8192,11 +8174,11 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Use of counseling/therapy</t>
+          <t>Satisfaction with counseling/therapy</t>
         </is>
       </c>
       <c r="D12" s="7" t="n">
@@ -8204,7 +8186,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? [pipe in selected options from the question, “From which of the following places did you receive counseling or therapy?”]</t>
+          <t>How satisfied/dissatisfied are you with your overall therapy or counseling experience?</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -8214,17 +8196,17 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>1=In-person only 2=Remote/telehealth only (digital video conferencing, text/app chat, etc…) 3=Both in-person and remote</t>
+          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Matrix</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr"/>
@@ -8240,12 +8222,12 @@
       <c r="R12" s="7" t="inlineStr"/>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
         </is>
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8236,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -8266,7 +8248,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with your overall therapy or counseling experience?</t>
+          <t>How satisfied/dissatisfied are you with the telemental health services you have received from the following providers? [pipe in the selected options remote/both in-person &amp; remote from the question: Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?]</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -8276,7 +8258,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -8302,12 +8284,12 @@
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
+          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
+          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8298,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -8328,7 +8310,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with the telemental health services you have received from the following providers? [pipe in the selected options remote/both in-person &amp; remote from the question: Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?]</t>
+          <t>How helpful, overall, do you think therapy or counseling was or has been for your mental or emotional health?</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -8338,17 +8320,17 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
+          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Categorical (Ordinal)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -8364,161 +8346,161 @@
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Satisfaction with counseling/therapy</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="B15" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Use of medication</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>How helpful, overall, do you think therapy or counseling was or has been for your mental or emotional health?</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>In the past 12 months have you taken any of the following types of prescription medications? (Please count only those you took, or are taking, several times per week.) (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Knowledge/Memory, Reading, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr"/>
+      <c r="T15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Use of medication</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Follow-up Question</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="n">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Use of medication</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>In the past 12 months have you taken any of the following types of prescription medications? (Please count only those you took, or are taking, several times per week.) (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Reading, Response Categories</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr"/>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -8530,7 +8512,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
+          <t>For what reason(s) do you use Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) (Select all that apply)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -8566,12 +8548,12 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8580,7 +8562,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -8592,7 +8574,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>For what reason(s) do you use Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) (Select all that apply)</t>
+          <t>In the past 12 months how many times have you discussed with a doctor or other health professional your use of the medication(s) you just noted?</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -8607,12 +8589,12 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Likert (5-point)</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -8628,12 +8610,12 @@
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8624,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -8654,7 +8636,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>In the past 12 months how many times have you discussed with a doctor or other health professional your use of the medication(s) you just noted?</t>
+          <t>Who wrote your most recent prescription for the medication(s) you noted in the last question? (Select all that apply)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -8669,12 +8651,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
+          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Likert (5-point)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -8704,7 +8686,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -8716,7 +8698,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Who wrote your most recent prescription for the medication(s) you noted in the last question? (Select all that apply)</t>
+          <t>In the past 12 months, have you used your prescription stimulant (e.g., Ritalin, Adderall) in any way not directed by a doctor (e.g., use in greater amounts or more often than directed)?</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -8731,12 +8713,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
+          <t>1=Yes 2=No</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -8752,12 +8734,12 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8748,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -8778,7 +8760,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>In the past 12 months, have you used your prescription stimulant (e.g., Ritalin, Adderall) in any way not directed by a doctor (e.g., use in greater amounts or more often than directed)?</t>
+          <t>In the past 12 months, have you given away, traded, or sold your prescription stimulant (e.g., Ritalin, Adderall)?</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -8828,7 +8810,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -8840,7 +8822,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>In the past 12 months, have you given away, traded, or sold your prescription stimulant (e.g., Ritalin, Adderall)?</t>
+          <t>Where is the prescriber located who wrote most of the prescriptions for your stimulant in the past 12 months?</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -8855,12 +8837,12 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>1=Yes 2=No</t>
+          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Others</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr"/>
@@ -8890,7 +8872,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -8902,7 +8884,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>Where is the prescriber located who wrote most of the prescriptions for your stimulant in the past 12 months?</t>
+          <t>How helpful, overall, do you think the medication(s) was or has been for your mental or emotional health?</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -8917,12 +8899,12 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Others</t>
+          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Categorical (Ordinal)</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr"/>
@@ -8938,12 +8920,12 @@
       <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
     </row>
@@ -8952,7 +8934,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -8964,7 +8946,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>How helpful, overall, do you think the medication(s) was or has been for your mental or emotional health?</t>
+          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -8974,17 +8956,17 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>31; 22</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
+          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Ordinal)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
@@ -9000,74 +8982,96 @@
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
         </is>
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>43</v>
-      </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>Use of medication</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>31; 22</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="I25" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr"/>
-      <c r="K25" s="7" t="inlineStr"/>
-      <c r="L25" s="7" t="inlineStr"/>
-      <c r="M25" s="7" t="inlineStr"/>
-      <c r="N25" s="7" t="inlineStr"/>
-      <c r="O25" s="7" t="inlineStr"/>
-      <c r="P25" s="7" t="inlineStr"/>
-      <c r="Q25" s="7" t="n">
+      <c r="B25" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Knowledge of campus services</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>How much do you agree with the following statement? If I needed to seek professional help for my mental or emotional health, I would know where to access resources from my school.</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Likert (6-point)</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>52.45</v>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="R25" s="7" t="inlineStr"/>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
-        </is>
-      </c>
-      <c r="T25" s="7" t="inlineStr">
-        <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
+      <c r="O25" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="inlineStr">
+        <is>
+          <t>Reading, Response Categories, Sensitivity/Bias</t>
+        </is>
+      </c>
+      <c r="Q25" s="5" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="R25" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S25" s="5" t="inlineStr">
+        <is>
+          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
+        </is>
+      </c>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
         </is>
       </c>
     </row>
@@ -9076,17 +9080,17 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Knowledge of campus services</t>
+          <t>Help-seeking intentions</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>How much do you agree with the following statement? If I needed to seek professional help for my mental or emotional health, I would know where to access resources from my school.</t>
+          <t>If you were experiencing serious emotional distress, whom would you talk to about this? (Select all that apply)</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -9097,20 +9101,20 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>52.45</v>
+        <v>28.36</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -9133,44 +9137,36 @@
       </c>
       <c r="P26" s="5" t="inlineStr">
         <is>
-          <t>Reading, Response Categories, Sensitivity/Bias</t>
+          <t>Assumptions, Response Categories, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>0.345</v>
+        <v>0.393</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
-        </is>
-      </c>
+      <c r="S26" s="5" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Help-seeking intentions</t>
+          <t>Use of medication</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>If you were experiencing serious emotional distress, whom would you talk to about this? (Select all that apply)</t>
+          <t>Within the last 12 months, how has ADHD affected your academic performance?</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -9181,7 +9177,7 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
+          <t>1=It has not impaired my academic performance 2=It has minimally impaired my academic performance 3=It has moderately impaired my academic performance 4=It has significantly impaired my academic performance</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -9190,7 +9186,7 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>28.36</v>
+        <v>4.14</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -9212,31 +9208,39 @@
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>Assumptions, Response Categories, Sensitivity/Bias</t>
+          <t>Response Categories</t>
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.393</v>
+        <v>0.425</v>
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
@@ -9246,7 +9250,7 @@
       <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Within the last 12 months, how has ADHD affected your academic performance?</t>
+          <t>Of the medication(s) you just noted, which are you currently taking? (Select all that apply)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -9257,7 +9261,7 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>1=It has not impaired my academic performance 2=It has minimally impaired my academic performance 3=It has moderately impaired my academic performance 4=It has significantly impaired my academic performance</t>
+          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -9266,7 +9270,7 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>4.14</v>
+        <v>0</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -9297,7 +9301,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>0.425</v>
+        <v>0.433</v>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
@@ -9306,31 +9310,27 @@
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
-        </is>
-      </c>
-      <c r="T28" s="5" t="inlineStr">
-        <is>
-          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
-        </is>
-      </c>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
+      <c r="T28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Use of medication</t>
+          <t>Satisfaction with counseling/therapy</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr"/>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Of the medication(s) you just noted, which are you currently taking? (Select all that apply)</t>
+          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -9341,224 +9341,206 @@
       <c r="G29" s="5" t="inlineStr"/>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
+          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>26.69</v>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O29" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="inlineStr">
+        <is>
+          <t>Knowledge/Memory, Reading</t>
+        </is>
+      </c>
+      <c r="Q29" s="5" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="R29" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S29" s="5" t="inlineStr">
+        <is>
+          <t>One matrix table question with 6 statements for each option selected for “From which of the following places did you receive counseling or therapy?” (Up to 8)</t>
+        </is>
+      </c>
+      <c r="T29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Diagnosed mental illnesses</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>Have you ever been diagnosed with any of the following conditions by a health professional (e.g., primary care doctor, psychiatrist, psychologist, etc.)? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="K30" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="n">
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="O30" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="R29" s="5" t="inlineStr">
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Reading, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Satisfaction with counseling/therapy</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Matrix</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L30" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M30" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O30" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Reading</t>
-        </is>
-      </c>
-      <c r="Q30" s="5" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="R30" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S30" s="5" t="inlineStr">
-        <is>
-          <t>One matrix table question with 6 statements for each option selected for “From which of the following places did you receive counseling or therapy?” (Up to 8)</t>
-        </is>
-      </c>
-      <c r="T30" s="5" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
+      <c r="T30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="n">
+      <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Diagnosed mental illnesses</t>
         </is>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>Have you ever been diagnosed with any of the following conditions by a health professional (e.g., primary care doctor, psychiatrist, psychologist, etc.)? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr">
-        <is>
-          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
-        </is>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>Specifically, which of the following depressive disorders were you diagnosed with by a professional? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Other (please specify) 5=Don’t know</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J31" s="6" t="n">
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr"/>
+      <c r="Q31" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L31" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M31" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>Reading, Response Categories</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S31" s="6" t="inlineStr"/>
-      <c r="T31" s="6" t="inlineStr"/>
+      <c r="R31" s="7" t="inlineStr"/>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+        </is>
+      </c>
+      <c r="T31" s="7" t="inlineStr">
+        <is>
+          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -9570,7 +9552,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following depressive disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following bipolar and related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -9585,7 +9567,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Other (please specify) 5=Don’t know</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -9606,12 +9588,12 @@
       <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9620,7 +9602,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -9632,7 +9614,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following bipolar and related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following anxiety disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -9647,7 +9629,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -9668,12 +9650,12 @@
       <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9664,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -9694,7 +9676,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following anxiety disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following obsessive-compulsive or related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -9709,7 +9691,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -9730,12 +9712,12 @@
       <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9744,7 +9726,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -9756,7 +9738,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following obsessive-compulsive or related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following trauma and stressor related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -9771,7 +9753,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Other (please specify) 5=Don’t know</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -9792,12 +9774,12 @@
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9806,7 +9788,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -9818,7 +9800,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following trauma and stressor related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -9833,7 +9815,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Other (please specify) 5=Don’t know</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -9854,12 +9836,12 @@
       <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9868,7 +9850,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -9880,7 +9862,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following eating disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -9895,7 +9877,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -9916,12 +9898,12 @@
       <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9930,7 +9912,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -9942,7 +9924,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following eating disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following psychotic disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -9957,7 +9939,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -9978,12 +9960,12 @@
       <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
-          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9992,7 +9974,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -10004,7 +9986,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following psychotic disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following personality disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -10019,7 +10001,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Other (please specify) 12=Don’t know</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -10040,12 +10022,12 @@
       <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10036,7 @@
         <v>39</v>
       </c>
       <c r="B40" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
@@ -10066,7 +10048,7 @@
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following personality disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following substance disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -10081,7 +10063,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Other (please specify) 12=Don’t know</t>
+          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Other (please specify) 3=Don’t know</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -10102,154 +10084,154 @@
       <c r="R40" s="7" t="inlineStr"/>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T40" s="7" t="inlineStr">
         <is>
-          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="n">
+      <c r="A41" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C41" s="7" t="inlineStr">
-        <is>
-          <t>Diagnosed mental illnesses</t>
-        </is>
-      </c>
-      <c r="D41" s="7" t="n">
+      <c r="B41" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Disability</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>Specifically, which of the following substance disorders were you diagnosed with by a professional? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>Do you have a disability or disabilities from any of the following categories? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr"/>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Other (please specify) 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L41" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S41" s="6" t="inlineStr"/>
+      <c r="T41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Disability</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>Are you registered with the office for disability services/ADA office on this campus as having a disability?</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>Follow-up Question</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Other (please specify) 3=Don’t know</t>
-        </is>
-      </c>
-      <c r="I41" s="7" t="inlineStr">
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>1=Yes 2=No 3=Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J41" s="7" t="inlineStr"/>
-      <c r="K41" s="7" t="inlineStr"/>
-      <c r="L41" s="7" t="inlineStr"/>
-      <c r="M41" s="7" t="inlineStr"/>
-      <c r="N41" s="7" t="inlineStr"/>
-      <c r="O41" s="7" t="inlineStr"/>
-      <c r="P41" s="7" t="inlineStr"/>
-      <c r="Q41" s="7" t="n">
+      <c r="J42" s="7" t="inlineStr"/>
+      <c r="K42" s="7" t="inlineStr"/>
+      <c r="L42" s="7" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+      <c r="N42" s="7" t="inlineStr"/>
+      <c r="O42" s="7" t="inlineStr"/>
+      <c r="P42" s="7" t="inlineStr"/>
+      <c r="Q42" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R41" s="7" t="inlineStr"/>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
-        </is>
-      </c>
-      <c r="T41" s="7" t="inlineStr">
-        <is>
-          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>Disability</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>Do you have a disability or disabilities from any of the following categories? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6" t="inlineStr">
-        <is>
-          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Other (please specify) 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L42" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M42" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N42" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S42" s="6" t="inlineStr"/>
-      <c r="T42" s="6" t="inlineStr"/>
+      <c r="R42" s="7" t="inlineStr"/>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+        </is>
+      </c>
+      <c r="T42" s="7" t="inlineStr">
+        <is>
+          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -1188,36 +1188,36 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>8.289999999999999</v>
+        <v>7.35</v>
       </c>
       <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Insurance</t>
+          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Disability</t>
+          <t xml:space="preserve">  ↳ Insurance</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Disability</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1228,34 +1228,34 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
+          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.34</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
+          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.51</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="50">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.64</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="55">
@@ -7706,12 +7706,12 @@
       <c r="R4" s="7" t="inlineStr"/>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
       <c r="T4" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
     </row>
@@ -7768,12 +7768,12 @@
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8236,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with the telemental health services you have received from the following providers? [pipe in the selected options remote/both in-person &amp; remote from the question: Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?]</t>
+          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
@@ -8284,12 +8284,12 @@
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8298,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -8310,7 +8310,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>How helpful, overall, do you think therapy or counseling was or has been for your mental or emotional health?</t>
+          <t>How satisfied/dissatisfied are you with the telemental health services you have received from the following providers? [pipe in the selected options remote/both in-person &amp; remote from the question: Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?]</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
+          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Ordinal)</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -8346,161 +8346,161 @@
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="7" t="inlineStr">
         <is>
+          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Satisfaction with counseling/therapy</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>How helpful, overall, do you think therapy or counseling was or has been for your mental or emotional health?</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr"/>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
           <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
         </is>
       </c>
-      <c r="T14" s="7" t="inlineStr">
+      <c r="T15" s="7" t="inlineStr">
         <is>
           <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="6" t="n">
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="6" t="n">
         <v>31</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Use of medication</t>
         </is>
       </c>
-      <c r="D15" s="6" t="n">
+      <c r="D16" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>In the past 12 months have you taken any of the following types of prescription medications? (Please count only those you took, or are taking, several times per week.) (Select all that apply)</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>Mother Question</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="6" t="inlineStr">
         <is>
           <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
         </is>
       </c>
-      <c r="I15" s="6" t="inlineStr">
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J15" s="6" t="n">
+      <c r="J16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="K15" s="6" t="inlineStr">
+      <c r="K16" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M15" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="n">
+      <c r="L16" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O15" s="6" t="inlineStr">
+      <c r="O16" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="P15" s="6" t="inlineStr">
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>Knowledge/Memory, Reading, Response Categories</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="n">
+      <c r="Q16" s="6" t="n">
         <v>0.6</v>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="S15" s="6" t="inlineStr"/>
-      <c r="T15" s="6" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="n">
-        <v>32</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Use of medication</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="I16" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
-      <c r="M16" s="7" t="inlineStr"/>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr"/>
-      <c r="P16" s="7" t="inlineStr"/>
-      <c r="Q16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="7" t="inlineStr"/>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr">
-        <is>
-          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
+      <c r="S16" s="6" t="inlineStr"/>
+      <c r="T16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -8512,7 +8512,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>For what reason(s) do you use Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) (Select all that apply)</t>
+          <t>For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -8548,12 +8548,12 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8562,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>In the past 12 months how many times have you discussed with a doctor or other health professional your use of the medication(s) you just noted?</t>
+          <t>For what reason(s) do you use Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) (Select all that apply)</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
+          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Likert (5-point)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -8610,12 +8610,12 @@
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8624,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>Who wrote your most recent prescription for the medication(s) you noted in the last question? (Select all that apply)</t>
+          <t>In the past 12 months how many times have you discussed with a doctor or other health professional your use of the medication(s) you just noted?</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
+          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Likert (5-point)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -8686,7 +8686,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -8698,7 +8698,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>In the past 12 months, have you used your prescription stimulant (e.g., Ritalin, Adderall) in any way not directed by a doctor (e.g., use in greater amounts or more often than directed)?</t>
+          <t>Who wrote your most recent prescription for the medication(s) you noted in the last question? (Select all that apply)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1=Yes 2=No</t>
+          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr"/>
@@ -8734,12 +8734,12 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="7" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>In the past 12 months, have you given away, traded, or sold your prescription stimulant (e.g., Ritalin, Adderall)?</t>
+          <t>In the past 12 months, have you used your prescription stimulant (e.g., Ritalin, Adderall) in any way not directed by a doctor (e.g., use in greater amounts or more often than directed)?</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -8810,7 +8810,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>Where is the prescriber located who wrote most of the prescriptions for your stimulant in the past 12 months?</t>
+          <t>In the past 12 months, have you given away, traded, or sold your prescription stimulant (e.g., Ritalin, Adderall)?</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Others</t>
+          <t>1=Yes 2=No</t>
         </is>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr"/>
@@ -8872,7 +8872,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
@@ -8884,7 +8884,7 @@
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>How helpful, overall, do you think the medication(s) was or has been for your mental or emotional health?</t>
+          <t>Where is the prescriber located who wrote most of the prescriptions for your stimulant in the past 12 months?</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
+          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Others</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Ordinal)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J23" s="7" t="inlineStr"/>
@@ -8920,12 +8920,12 @@
       <c r="R23" s="7" t="inlineStr"/>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
       <c r="T23" s="7" t="inlineStr">
         <is>
-          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Display if "1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.)" is selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -8946,7 +8946,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
+          <t>How helpful, overall, do you think the medication(s) was or has been for your mental or emotional health?</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -8956,17 +8956,17 @@
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>31; 22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
+          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Categorical (Ordinal)</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
@@ -8982,96 +8982,74 @@
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="7" t="inlineStr">
         <is>
+          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>Use of medication</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>31; 22</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
           <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
         </is>
       </c>
-      <c r="T24" s="7" t="inlineStr">
+      <c r="T25" s="7" t="inlineStr">
         <is>
           <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Knowledge of campus services</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>How much do you agree with the following statement? If I needed to seek professional help for my mental or emotional health, I would know where to access resources from my school.</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr"/>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Likert (6-point)</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>52.45</v>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L25" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M25" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="inlineStr">
-        <is>
-          <t>Reading, Response Categories, Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="Q25" s="5" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="R25" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S25" s="5" t="inlineStr">
-        <is>
-          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
-        </is>
-      </c>
-      <c r="T25" s="5" t="inlineStr">
-        <is>
-          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
         </is>
       </c>
     </row>
@@ -9080,17 +9058,17 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>Help-seeking intentions</t>
+          <t>Knowledge of campus services</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr"/>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>If you were experiencing serious emotional distress, whom would you talk to about this? (Select all that apply)</t>
+          <t>How much do you agree with the following statement? If I needed to seek professional help for my mental or emotional health, I would know where to access resources from my school.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
@@ -9101,20 +9079,20 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>28.36</v>
+        <v>52.45</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L26" s="5" t="inlineStr">
@@ -9137,36 +9115,44 @@
       </c>
       <c r="P26" s="5" t="inlineStr">
         <is>
-          <t>Assumptions, Response Categories, Sensitivity/Bias</t>
+          <t>Reading, Response Categories, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>0.393</v>
+        <v>0.345</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S26" s="5" t="inlineStr"/>
-      <c r="T26" s="5" t="inlineStr"/>
+      <c r="S26" s="5" t="inlineStr">
+        <is>
+          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
+        </is>
+      </c>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Use of medication</t>
+          <t>Help-seeking intentions</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Within the last 12 months, how has ADHD affected your academic performance?</t>
+          <t>If you were experiencing serious emotional distress, whom would you talk to about this? (Select all that apply)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -9177,7 +9163,7 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>1=It has not impaired my academic performance 2=It has minimally impaired my academic performance 3=It has moderately impaired my academic performance 4=It has significantly impaired my academic performance</t>
+          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
@@ -9186,7 +9172,7 @@
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>4.14</v>
+        <v>28.36</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
@@ -9208,32 +9194,24 @@
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>Response Categories</t>
+          <t>Assumptions, Response Categories, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.425</v>
+        <v>0.393</v>
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S27" s="5" t="inlineStr">
-        <is>
-          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
-        </is>
-      </c>
-      <c r="T27" s="5" t="inlineStr">
-        <is>
-          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
-        </is>
-      </c>
+      <c r="S27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
@@ -9316,169 +9294,151 @@
       <c r="T28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="6" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="5" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Satisfaction with counseling/therapy</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
-        </is>
-      </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Matrix</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Diagnosed mental illnesses</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>Have you ever been diagnosed with any of the following conditions by a health professional (e.g., primary care doctor, psychiatrist, psychologist, etc.)? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Reading, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N29" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O29" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Reading</t>
-        </is>
-      </c>
-      <c r="Q29" s="5" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="R29" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S29" s="5" t="inlineStr">
-        <is>
-          <t>One matrix table question with 6 statements for each option selected for “From which of the following places did you receive counseling or therapy?” (Up to 8)</t>
-        </is>
-      </c>
-      <c r="T29" s="5" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
+      <c r="T29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="n">
+      <c r="A30" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>Diagnosed mental illnesses</t>
         </is>
       </c>
-      <c r="D30" s="6" t="n">
+      <c r="D30" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>Have you ever been diagnosed with any of the following conditions by a health professional (e.g., primary care doctor, psychiatrist, psychologist, etc.)? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6" t="inlineStr">
-        <is>
-          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
-        </is>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Specifically, which of the following depressive disorders were you diagnosed with by a professional? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Other (please specify) 5=Don’t know</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J30" s="6" t="n">
+      <c r="J30" s="7" t="inlineStr"/>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+      <c r="N30" s="7" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr"/>
+      <c r="Q30" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M30" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N30" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>Reading, Response Categories</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v>0.517</v>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S30" s="6" t="inlineStr"/>
-      <c r="T30" s="6" t="inlineStr"/>
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
+        <is>
+          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
@@ -9490,7 +9450,7 @@
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following depressive disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following bipolar and related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -9505,7 +9465,7 @@
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Other (please specify) 5=Don’t know</t>
         </is>
       </c>
       <c r="I31" s="7" t="inlineStr">
@@ -9526,12 +9486,12 @@
       <c r="R31" s="7" t="inlineStr"/>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T31" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9500,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
@@ -9552,7 +9512,7 @@
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following bipolar and related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following anxiety disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -9567,7 +9527,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -9588,12 +9548,12 @@
       <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9562,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -9614,7 +9574,7 @@
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following anxiety disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following obsessive-compulsive or related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -9629,7 +9589,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -9650,12 +9610,12 @@
       <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9664,7 +9624,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -9676,7 +9636,7 @@
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following obsessive-compulsive or related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following trauma and stressor related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -9691,7 +9651,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Other (please specify) 5=Don’t know</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -9712,12 +9672,12 @@
       <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9726,7 +9686,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -9738,7 +9698,7 @@
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following trauma and stressor related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -9753,7 +9713,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Other (please specify) 5=Don’t know</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -9774,12 +9734,12 @@
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9748,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -9800,7 +9760,7 @@
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following eating disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -9815,7 +9775,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -9836,12 +9796,12 @@
       <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9810,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -9862,7 +9822,7 @@
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following eating disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following psychotic disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -9877,7 +9837,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Other (please specify) 7=Don’t know</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -9898,12 +9858,12 @@
       <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9912,7 +9872,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -9924,7 +9884,7 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following psychotic disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following personality disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -9939,7 +9899,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Other (please specify) 12=Don’t know</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -9960,12 +9920,12 @@
       <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9974,7 +9934,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -9986,7 +9946,7 @@
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following personality disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following substance disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -10001,7 +9961,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Other (please specify) 12=Don’t know</t>
+          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Other (please specify) 3=Don’t know</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -10022,161 +9982,161 @@
       <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="n">
+      <c r="A40" s="6" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C40" s="7" t="inlineStr">
-        <is>
-          <t>Diagnosed mental illnesses</t>
-        </is>
-      </c>
-      <c r="D40" s="7" t="n">
+      <c r="B40" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Disability</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E40" s="7" t="inlineStr">
-        <is>
-          <t>Specifically, which of the following substance disorders were you diagnosed with by a professional? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>Do you have a disability or disabilities from any of the following categories? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr"/>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Other (please specify) 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L40" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S40" s="6" t="inlineStr"/>
+      <c r="T40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>Disability</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>Are you registered with the office for disability services/ADA office on this campus as having a disability?</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>Follow-up Question</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Other (please specify) 3=Don’t know</t>
-        </is>
-      </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>1=Yes 2=No 3=Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J40" s="7" t="inlineStr"/>
-      <c r="K40" s="7" t="inlineStr"/>
-      <c r="L40" s="7" t="inlineStr"/>
-      <c r="M40" s="7" t="inlineStr"/>
-      <c r="N40" s="7" t="inlineStr"/>
-      <c r="O40" s="7" t="inlineStr"/>
-      <c r="P40" s="7" t="inlineStr"/>
-      <c r="Q40" s="7" t="n">
+      <c r="J41" s="7" t="inlineStr"/>
+      <c r="K41" s="7" t="inlineStr"/>
+      <c r="L41" s="7" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+      <c r="N41" s="7" t="inlineStr"/>
+      <c r="O41" s="7" t="inlineStr"/>
+      <c r="P41" s="7" t="inlineStr"/>
+      <c r="Q41" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R40" s="7" t="inlineStr"/>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
-        </is>
-      </c>
-      <c r="T40" s="7" t="inlineStr">
-        <is>
-          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>Disability</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>Do you have a disability or disabilities from any of the following categories? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Other (please specify) 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L41" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M41" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S41" s="6" t="inlineStr"/>
-      <c r="T41" s="6" t="inlineStr"/>
+      <c r="R41" s="7" t="inlineStr"/>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+        </is>
+      </c>
+      <c r="T41" s="7" t="inlineStr">
+        <is>
+          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
@@ -10188,7 +10148,7 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>Are you registered with the office for disability services/ADA office on this campus as having a disability?</t>
+          <t>When were you diagnosed with ADHD ?</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -10198,17 +10158,17 @@
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7; 12</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>1=Yes 2=No 3=Prefer not to say</t>
+          <t>0=Prior to starting college 1=After starting college</t>
         </is>
       </c>
       <c r="I42" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="J42" s="7" t="inlineStr"/>
@@ -10224,12 +10184,12 @@
       <c r="R42" s="7" t="inlineStr"/>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
         </is>
       </c>
       <c r="T42" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10198,7 @@
         <v>42</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
@@ -10250,7 +10210,7 @@
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>When were you diagnosed with ADHD ?</t>
+          <t>What type of treatment for ADHD have you received in the past year?</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -10260,17 +10220,17 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>7; 12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>0=Prior to starting college 1=After starting college</t>
+          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Other (please specify)</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J43" s="7" t="inlineStr"/>
@@ -10286,12 +10246,12 @@
       <c r="R43" s="7" t="inlineStr"/>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
+          <t>Display if previous question is displayed</t>
         </is>
       </c>
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
+          <t>Display if previous question is displayed</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10260,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
@@ -10312,7 +10272,7 @@
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>What type of treatment for ADHD have you received in the past year?</t>
+          <t>What type of treatment for ADHD did you receive prior to starting college?</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -10348,12 +10308,12 @@
       <c r="R44" s="7" t="inlineStr"/>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>Display if previous question is displayed</t>
+          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
         </is>
       </c>
       <c r="T44" s="7" t="inlineStr">
         <is>
-          <t>Display if previous question is displayed</t>
+          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
         </is>
       </c>
     </row>
@@ -10362,11 +10322,11 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Disability</t>
+          <t>Use of medication</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
@@ -10374,7 +10334,7 @@
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>What type of treatment for ADHD did you receive prior to starting college?</t>
+          <t>Within the last 12 months, how has ADHD affected your academic performance?</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -10384,12 +10344,12 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Other (please specify)</t>
+          <t>1=It has not impaired my academic performance 2=It has minimally impaired my academic performance 3=It has moderately impaired my academic performance 4=It has significantly impaired my academic performance</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -10410,12 +10370,12 @@
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
         </is>
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
         </is>
       </c>
     </row>
@@ -10550,12 +10510,12 @@
       <c r="R47" s="7" t="inlineStr"/>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “8=No, none of these” is selected for “In the past 12 months, have you received support for your mental or emotional health from any of the following sources?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
         </is>
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>Display if any option other than “8=No, none of these” is selected for “In the past 12 months, have you received support for your mental or emotional health from any of the following sources?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -8899,7 +8899,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Others</t>
+          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other (please specify)</t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -10344,7 +10344,7 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7; 12</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -10370,12 +10370,12 @@
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -80,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,32 +91,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1188,7 +1199,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7.35</v>
+        <v>6.74</v>
       </c>
       <c r="C43" t="inlineStr"/>
     </row>
@@ -1272,45 +1283,45 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Stigma</t>
+          <t xml:space="preserve">  ↳ Use of medication</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Perceived need</t>
+          <t xml:space="preserve">  ↳ Stigma</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
+          <t xml:space="preserve">  ↳ Perceived need</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>1.17</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of medication</t>
+          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="55">
@@ -7492,173 +7503,155 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="n">
-        <v>41</v>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Use of medication</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr"/>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>During the past year, for how long, in total, have you taken the following medication(s)?</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr"/>
-      <c r="H2" s="5" t="inlineStr">
-        <is>
-          <t>1=Less than 1 month 2=Between 1 and 2 months 3=2 months or more 4=Did not take</t>
-        </is>
-      </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>84.01000000000001</v>
-      </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N2" s="5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>What is the source of your current health insurance coverage? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have health insurance through an embassy or sponsoring agency for international students. 7=I have individual health insurance purchased directly from an insurance carrier. 8=I have Medicaid or other governmental insurance. 9=I am uncertain about whether I have health insurance. 10=I have health insurance but am uncertain about where it is from.</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>33.45</v>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q2" s="5" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="R2" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S2" s="5" t="inlineStr">
-        <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
-      <c r="T2" s="5" t="inlineStr"/>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S2" s="6" t="inlineStr">
+        <is>
+          <t>RANDOM 2</t>
+        </is>
+      </c>
+      <c r="T2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="B3" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D3" s="6" t="n">
+      <c r="D3" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
-        <is>
-          <t>What is the source of your current health insurance coverage? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have health insurance through an embassy or sponsoring agency for international students. 7=I have individual health insurance purchased directly from an insurance carrier. 8=I have Medicaid or other governmental insurance. 9=I am uncertain about whether I have health insurance. 10=I have health insurance but am uncertain about where it is from.</t>
-        </is>
-      </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>Do you know if your health insurance plan would provide any coverage for a visit to a mental health professional (such as a psychiatrist, psychologist, clinical social worker, etc.)?</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>1=Yes, it definitely would. 2=I think it would but am not sure. 3=I have no idea. 4=I think it would not but am not sure. 5=No, it definitely would not.</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J3" s="6" t="n">
-        <v>33.45</v>
-      </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M3" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N3" s="6" t="n">
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr"/>
+      <c r="P3" s="7" t="inlineStr"/>
+      <c r="Q3" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S3" s="6" t="inlineStr">
-        <is>
-          <t>RANDOM 2</t>
-        </is>
-      </c>
-      <c r="T3" s="6" t="inlineStr"/>
+      <c r="R3" s="7" t="inlineStr"/>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
+        <is>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
@@ -7670,7 +7663,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>Do you know if your health insurance plan would provide any coverage for a visit to a mental health professional (such as a psychiatrist, psychologist, clinical social worker, etc.)?</t>
+          <t>Does your current health insurance plan meet your needs for mental health services?</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -7685,7 +7678,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>1=Yes, it definitely would. 2=I think it would but am not sure. 3=I have no idea. 4=I think it would not but am not sure. 5=No, it definitely would not.</t>
+          <t>1=I have not needed to use my current insurance plan to cover mental health services. 2=Yes, everything I have needed is covered. 3=No, the coverage is inadequate to meet my needs. 4=I’m not sure</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -7720,7 +7713,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -7732,7 +7725,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>Does your current health insurance plan meet your needs for mental health services?</t>
+          <t>I feel that coverage is inadequate because my plan… (Select all that apply)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -7742,12 +7735,12 @@
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>1=I have not needed to use my current insurance plan to cover mental health services. 2=Yes, everything I have needed is covered. 3=No, the coverage is inadequate to meet my needs. 4=I’m not sure</t>
+          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Other (please specify)</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -7768,165 +7761,165 @@
       <c r="R5" s="7" t="inlineStr"/>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
+          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
         </is>
       </c>
       <c r="T5" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
+          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>54</v>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7" t="inlineStr">
-        <is>
-          <t>I feel that coverage is inadequate because my plan… (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="B6" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Use of counseling/therapy</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Have you ever received counseling or therapy for mental health concerns?</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>1=No, never 2=Yes, prior to starting at this school 3=Yes, since starting at this school 4=Yes, both of the above (prior to and since starting at this school)</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>75.27</v>
+      </c>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>Sensitivity/Bias</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S6" s="6" t="inlineStr">
+        <is>
+          <t>CCMH Standardized Data Set</t>
+        </is>
+      </c>
+      <c r="T6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <v>23</v>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Use of counseling/therapy</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>How many total visits or sessions for counseling or therapy have you had in the past 12 months?</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Follow-up Question</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J6" s="7" t="inlineStr"/>
-      <c r="K6" s="7" t="inlineStr"/>
-      <c r="L6" s="7" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
-      <c r="N6" s="7" t="inlineStr"/>
-      <c r="O6" s="7" t="inlineStr"/>
-      <c r="P6" s="7" t="inlineStr"/>
-      <c r="Q6" s="7" t="n">
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>0=0 1=1-3 2=4-6 3=7-9 4=10 or more</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="7" t="inlineStr"/>
+      <c r="L7" s="7" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
+      <c r="N7" s="7" t="inlineStr"/>
+      <c r="O7" s="7" t="inlineStr"/>
+      <c r="P7" s="7" t="inlineStr"/>
+      <c r="Q7" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="7" t="inlineStr"/>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
-        </is>
-      </c>
-      <c r="T6" s="7" t="inlineStr">
-        <is>
-          <t>Display if “No, the coverage is inadequate to meet my needs” is selected for “Does your current health insurance plan meet your needs for mental health services?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>22</v>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>Use of counseling/therapy</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>Have you ever received counseling or therapy for mental health concerns?</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr">
-        <is>
-          <t>1=No, never 2=Yes, prior to starting at this school 3=Yes, since starting at this school 4=Yes, both of the above (prior to and since starting at this school)</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>75.27</v>
-      </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L7" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M7" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>CCMH Standardized Data Set</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr"/>
+      <c r="R7" s="7" t="inlineStr"/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+        </is>
+      </c>
+      <c r="T7" s="7" t="inlineStr">
+        <is>
+          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
@@ -7938,7 +7931,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>How many total visits or sessions for counseling or therapy have you had in the past 12 months?</t>
+          <t>Are you currently receiving counseling or therapy?</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
@@ -7948,17 +7941,17 @@
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>0=0 1=1-3 2=4-6 3=7-9 4=10 or more</t>
+          <t>1=Yes 0=No</t>
         </is>
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Ordinal)</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="J8" s="7" t="inlineStr"/>
@@ -7974,12 +7967,12 @@
       <c r="R8" s="7" t="inlineStr"/>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
       <c r="T8" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Yes, prior to starting college”, “Yes, since starting college”, or “Yes, both of the above (prior to college and since starting college” is selected for “Have you ever received counseling or therapy for mental health concerns?”</t>
+          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
     </row>
@@ -7988,7 +7981,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -8000,7 +7993,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Are you currently receiving counseling or therapy?</t>
+          <t>From which of the following did you receive counseling or therapy in the past 12 months? (Select all that apply)</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -8010,17 +8003,17 @@
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24; 23</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>1=Yes 0=No</t>
+          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Other</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr"/>
@@ -8036,12 +8029,12 @@
       <c r="R9" s="7" t="inlineStr"/>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
       <c r="T9" s="7" t="inlineStr">
         <is>
-          <t>Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8043,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
@@ -8062,7 +8055,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>From which of the following did you receive counseling or therapy in the past 12 months? (Select all that apply)</t>
+          <t>Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? [pipe in selected options from the question, “From which of the following places did you receive counseling or therapy?”]</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -8072,17 +8065,17 @@
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>24; 23</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Other</t>
+          <t>1=In-person only 2=Remote/telehealth only (digital video conferencing, text/app chat, etc…) 3=Both in-person and remote</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr"/>
@@ -8098,12 +8091,12 @@
       <c r="R10" s="7" t="inlineStr"/>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
       <c r="T10" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Are you currently receiving counseling or therapy” is displayed. Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
         </is>
       </c>
     </row>
@@ -8112,11 +8105,11 @@
         <v>10</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Use of counseling/therapy</t>
+          <t>Satisfaction with counseling/therapy</t>
         </is>
       </c>
       <c r="D11" s="7" t="n">
@@ -8124,7 +8117,7 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? [pipe in selected options from the question, “From which of the following places did you receive counseling or therapy?”]</t>
+          <t>How satisfied/dissatisfied are you with your overall therapy or counseling experience?</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -8134,17 +8127,17 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>1=In-person only 2=Remote/telehealth only (digital video conferencing, text/app chat, etc…) 3=Both in-person and remote</t>
+          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
-          <t>Matrix</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J11" s="7" t="inlineStr"/>
@@ -8160,12 +8153,12 @@
       <c r="R11" s="7" t="inlineStr"/>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
         </is>
       </c>
       <c r="T11" s="7" t="inlineStr">
         <is>
-          <t>Matrix table question where the statements are the selected options for “From which of the following places did you receive counseling or therapy?” Display only if “How many total visits or sessions for counseling or therapy have you had in the past 12 months?” is not 0=0.</t>
+          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8167,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -8186,7 +8179,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with your overall therapy or counseling experience?</t>
+          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -8206,7 +8199,7 @@
       </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J12" s="7" t="inlineStr"/>
@@ -8222,12 +8215,12 @@
       <c r="R12" s="7" t="inlineStr"/>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
+          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
         </is>
       </c>
       <c r="T12" s="7" t="inlineStr">
         <is>
-          <t>Display only if “Have you ever received counseling or therapy for mental health concerns?” is not “No, Never.”</t>
+          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8229,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -8248,7 +8241,7 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
+          <t>How satisfied/dissatisfied are you with the telemental health services you have received from the following providers? [pipe in the selected options remote/both in-person &amp; remote from the question: Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?]</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -8258,7 +8251,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -8268,7 +8261,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Matrix</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J13" s="7" t="inlineStr"/>
@@ -8284,12 +8277,12 @@
       <c r="R13" s="7" t="inlineStr"/>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
+          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
         </is>
       </c>
       <c r="T13" s="7" t="inlineStr">
         <is>
-          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
+          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
         </is>
       </c>
     </row>
@@ -8298,7 +8291,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -8310,7 +8303,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with the telemental health services you have received from the following providers? [pipe in the selected options remote/both in-person &amp; remote from the question: Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?]</t>
+          <t>How helpful, overall, do you think therapy or counseling was or has been for your mental or emotional health?</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -8320,17 +8313,17 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
+          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Categorical (Ordinal)</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr"/>
@@ -8346,161 +8339,161 @@
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr">
         <is>
-          <t>Display if "remote" or "both in-person &amp; remote" is selected for "Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted?"</t>
+          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Satisfaction with counseling/therapy</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="n">
+      <c r="B15" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Use of medication</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>How helpful, overall, do you think therapy or counseling was or has been for your mental or emotional health?</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>In the past 12 months have you taken any of the following types of prescription medications? (Please count only those you took, or are taking, several times per week.) (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L15" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Knowledge/Memory, Reading, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr"/>
+      <c r="T15" s="6" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>Use of medication</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Follow-up Question</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr"/>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="n">
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Displayed if “No, never” is not selected for “Have you ever received counseling or therapy for your mental health?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>31</v>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>Use of medication</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>In the past 12 months have you taken any of the following types of prescription medications? (Please count only those you took, or are taking, several times per week.) (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
-        </is>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Reading, Response Categories</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr"/>
-      <c r="T16" s="6" t="inlineStr"/>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -8512,7 +8505,7 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>For what reason(s) do you use Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) ? (Select all that apply)</t>
+          <t>For what reason(s) do you use Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) (Select all that apply)</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -8548,12 +8541,12 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>If “1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexerdine), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8555,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
@@ -8574,7 +8567,7 @@
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>For what reason(s) do you use Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) (Select all that apply)</t>
+          <t>In the past 12 months how many times have you discussed with a doctor or other health professional your use of the medication(s) you just noted?</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -8589,12 +8582,12 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Likert (5-point)</t>
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr"/>
@@ -8610,12 +8603,12 @@
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Display if “4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (BuSpar), etc.)” is selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
         </is>
       </c>
     </row>
@@ -8624,7 +8617,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
@@ -8636,7 +8629,7 @@
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>In the past 12 months how many times have you discussed with a doctor or other health professional your use of the medication(s) you just noted?</t>
+          <t>Who wrote your most recent prescription for the medication(s) you noted in the last question? (Select all that apply)</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -8651,12 +8644,12 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
+          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
-          <t>Likert (5-point)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr"/>
@@ -8686,7 +8679,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
@@ -8698,7 +8691,7 @@
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>Who wrote your most recent prescription for the medication(s) you noted in the last question? (Select all that apply)</t>
+          <t>Of the medication(s) you just noted, which are you currently taking? (Select all that apply)</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -8713,7 +8706,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -8734,12 +8727,12 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8927,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="7" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
@@ -8946,7 +8939,7 @@
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>How helpful, overall, do you think the medication(s) was or has been for your mental or emotional health?</t>
+          <t>During the past year, for how long, in total, have you taken the following medication(s)?</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -8961,7 +8954,7 @@
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
+          <t>1=Less than 1 month 2=Between 1 and 2 months 3=2 months or more 4=Did not take</t>
         </is>
       </c>
       <c r="I24" s="7" t="inlineStr">
@@ -8982,12 +8975,12 @@
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8996,7 +8989,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="7" t="inlineStr">
         <is>
@@ -9008,7 +9001,7 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
+          <t>How helpful, overall, do you think the medication(s) was or has been for your mental or emotional health?</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -9018,17 +9011,17 @@
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>31; 22</t>
+          <t>31</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
+          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
         </is>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Categorical (Ordinal)</t>
         </is>
       </c>
       <c r="J25" s="7" t="inlineStr"/>
@@ -9044,96 +9037,74 @@
       <c r="R25" s="7" t="inlineStr"/>
       <c r="S25" s="7" t="inlineStr">
         <is>
+          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr">
+        <is>
+          <t>Displayed if "No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Use of medication</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>31; 22</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
           <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
         </is>
       </c>
-      <c r="T25" s="7" t="inlineStr">
+      <c r="T26" s="7" t="inlineStr">
         <is>
           <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" or "2=Yes, prior to starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "3=Yes, since starting at this school" is selected for "Have you ever received counseling or therapy for mental health concerns?" or "4=Yes, both of the above (prior to and since starting at this school)" is selected for "Have you ever received counseling or therapy for mental health concerns?"</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Knowledge of campus services</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>How much do you agree with the following statement? If I needed to seek professional help for my mental or emotional health, I would know where to access resources from my school.</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr"/>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>Likert (6-point)</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>52.45</v>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L26" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M26" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="inlineStr">
-        <is>
-          <t>Reading, Response Categories, Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="Q26" s="5" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="R26" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S26" s="5" t="inlineStr">
-        <is>
-          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
-        </is>
-      </c>
-      <c r="T26" s="5" t="inlineStr">
-        <is>
-          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
         </is>
       </c>
     </row>
@@ -9142,17 +9113,17 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>Help-seeking intentions</t>
+          <t>Knowledge of campus services</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr"/>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>If you were experiencing serious emotional distress, whom would you talk to about this? (Select all that apply)</t>
+          <t>How much do you agree with the following statement? If I needed to seek professional help for my mental or emotional health, I would know where to access resources from my school.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -9163,20 +9134,20 @@
       <c r="G27" s="5" t="inlineStr"/>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J27" s="5" t="n">
-        <v>28.36</v>
+        <v>52.45</v>
       </c>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L27" s="5" t="inlineStr">
@@ -9199,36 +9170,44 @@
       </c>
       <c r="P27" s="5" t="inlineStr">
         <is>
-          <t>Assumptions, Response Categories, Sensitivity/Bias</t>
+          <t>Reading, Response Categories, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>0.393</v>
+        <v>0.345</v>
       </c>
       <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S27" s="5" t="inlineStr"/>
-      <c r="T27" s="5" t="inlineStr"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
+        </is>
+      </c>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>Included if ‘Knowledge and Attitudes about Mental Health and Mental Health Services’ module not selected</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>Use of medication</t>
+          <t>Help-seeking intentions</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr"/>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Of the medication(s) you just noted, which are you currently taking? (Select all that apply)</t>
+          <t>If you were experiencing serious emotional distress, whom would you talk to about this? (Select all that apply)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
@@ -9239,7 +9218,7 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
+          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -9248,7 +9227,7 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>0</v>
+        <v>28.36</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -9270,27 +9249,23 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P28" s="5" t="inlineStr">
         <is>
-          <t>Response Categories</t>
+          <t>Assumptions, Response Categories, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>0.433</v>
+        <v>0.393</v>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
+      <c r="S28" s="5" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr"/>
     </row>
     <row r="29">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -11,9 +11,10 @@
     <sheet name="Overview" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Overall Health" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Financial Stress" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Academic Persistence, Retention" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Mental Health Status" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Mental Health Service Utilizati" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Academic Persistence, Retention" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Mental Health Status" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Mental Health Service Utilizati" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -695,7 +696,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -707,7 +708,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -722,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -847,491 +848,546 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Spending</t>
+          <t xml:space="preserve">  ↳ Scholarship Status</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Scholarship Status</t>
+          <t xml:space="preserve">  ↳ Housing concerns</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Housing concerns</t>
+          <t xml:space="preserve">  ↳ Financing education</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Financing education</t>
+          <t xml:space="preserve">  ↳ Socioeconomic status</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0.6</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Socioeconom ic status</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="n">
-        <v>1.44</v>
-      </c>
+          <t>Sheet1</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Academic Persistence, Retention</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Spending</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Faculty Advising (Ph D Students)</t>
+          <t xml:space="preserve">  ↳ Scholarship Status</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Overall social experience</t>
+          <t xml:space="preserve">  ↳ Housing concerns</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Imposter Syndrome</t>
+          <t xml:space="preserve">  ↳ Financing education</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0.36</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Clarifying achievement goals and their impact</t>
+          <t xml:space="preserve">  ↳ Socioeconomic status</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0.38</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Stress mindset</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="n">
-        <v>0.45</v>
-      </c>
+          <t>Academic Persistence, Retention</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Experiences with faculty and academic support services</t>
+          <t xml:space="preserve">  ↳ Faculty Advising (Ph D Students)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Perceived competition</t>
+          <t xml:space="preserve">  ↳ Overall social experience</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Issues affecting academic performance</t>
+          <t xml:space="preserve">  ↳ Imposter Syndrome</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.7</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Overall academic experience</t>
+          <t xml:space="preserve">  ↳ Clarifying achievement goals and their impact</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.46</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mental Health Status</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Stress mindset</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Eating and body image</t>
+          <t xml:space="preserve">  ↳ Experiences with faculty and academic support services</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Psychosis Screen</t>
+          <t xml:space="preserve">  ↳ Perceived competition</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.19</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Loneliness</t>
+          <t xml:space="preserve">  ↳ Issues affecting academic performance</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.28</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Social media/internet</t>
+          <t xml:space="preserve">  ↳ Overall academic experience</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.32</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Sleep</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="n">
-        <v>0.37</v>
-      </c>
+          <t>Mental Health Status</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="C32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Anxiety (GAD-7)</t>
+          <t xml:space="preserve">  ↳ Eating and body image</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>0.38</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Suicide Contagion</t>
+          <t xml:space="preserve">  ↳ Psychosis Screen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.38</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SDE</t>
+          <t xml:space="preserve">  ↳ Loneliness</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.4</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Substance use</t>
+          <t xml:space="preserve">  ↳ Social media/internet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Positive mental health</t>
+          <t xml:space="preserve">  ↳ Sleep</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0.41</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Academic Impairment</t>
+          <t xml:space="preserve">  ↳ Anxiety (GAD-7)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Non-suicidal self-injury</t>
+          <t xml:space="preserve">  ↳ Suicide Contagion</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>0.48</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Exercise</t>
+          <t xml:space="preserve">  ↳ SDE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.52</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Suicidality</t>
+          <t xml:space="preserve">  ↳ Substance use</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Depression (PHQ-9)</t>
+          <t xml:space="preserve">  ↳ Positive mental health</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>1.1</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mental Health Service Utilizati</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Academic Impairment</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Non-suicidal self-injury</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Insurance</t>
+          <t xml:space="preserve">  ↳ Exercise</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Disability</t>
+          <t xml:space="preserve">  ↳ Suicidality</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0.28</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Depression (PHQ-9)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.28</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="n">
-        <v>0.34</v>
-      </c>
+          <t>Mental Health Service Utilizati</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="C48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
+          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Diagnosed mental illnesses</t>
+          <t xml:space="preserve">  ↳ Insurance</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0.52</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of medication</t>
+          <t xml:space="preserve">  ↳ Disability</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0.6</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Stigma</t>
+          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.62</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Perceived need</t>
+          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.66</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
+          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.17</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Informal help-seeking</t>
+          <t xml:space="preserve">  ↳ Diagnosed mental illnesses</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ Use of medication</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ Stigma</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="n">
+        <v>0.62</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ Perceived need</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="n">
+        <v>1.17</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ↳ Informal help-seeking</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
+      <c r="C60" t="n">
         <v>1.66</v>
       </c>
     </row>
@@ -2654,6 +2710,900 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:T11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="40" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Delivery Order</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Source Question #</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Skip Group ID</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Question Role</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Parent Question #</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Response Type</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Flesch Reading Ease</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>FRE Band</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Blooms Score</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Response Option Complexity</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>Response Option Complexity Score</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Time-span and Sensitivity</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>QAS problems</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Cognitive Load Score</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Cognitive Load Band</t>
+        </is>
+      </c>
+      <c r="S1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="T1" s="4" t="inlineStr">
+        <is>
+          <t>Skip/Display Logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Housing concerns</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Do you have any concerns about your current living situation, like housing conditions, safety, and costs?</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>1=Yes 2=No</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="J2" s="6" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N2" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S2" s="6" t="inlineStr"/>
+      <c r="T2" s="6" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Housing concerns</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>What are those concerns? (Select all that apply.</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
+        <is>
+          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J3" s="7" t="inlineStr"/>
+      <c r="K3" s="7" t="inlineStr"/>
+      <c r="L3" s="7" t="inlineStr"/>
+      <c r="M3" s="7" t="inlineStr"/>
+      <c r="N3" s="7" t="inlineStr"/>
+      <c r="O3" s="7" t="inlineStr"/>
+      <c r="P3" s="7" t="inlineStr"/>
+      <c r="Q3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="7" t="inlineStr"/>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
+        </is>
+      </c>
+      <c r="T3" s="7" t="inlineStr">
+        <is>
+          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>How would you describe your financial situation right now?</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Likert (5-point)</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S4" s="5" t="inlineStr">
+        <is>
+          <t>CCMH Standardized Data Set</t>
+        </is>
+      </c>
+      <c r="T4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>How would you describe your financial situation while growing up?</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Likert (5-point)</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>CCMH Standardized Data Set</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Housing concerns</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources (please specify)</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>57</v>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Scholarship Status</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Do you receive scholarship funding from your institution? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="Q7" s="5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="R7" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Within the past 12 months the food I bought just didn’t last and I didn’t have money to get more.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>1=Often true 2=Sometimes true 3=Never true</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Knowledge/Memory</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>Within the past 12 months I worried whether our food would run out before we got money to buy more.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>1=Often true 2=Sometimes true 3=Never true</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Knowledge/Memory</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>Within the past 12 months, which of the following expenses have you had difficulty paying for? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>1=School 2=Food 3=Transportation 4=Childcare 5=Health care 6=Textbooks or course materials 7=Housing 8=None of the above [mutually exclusive]</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Knowledge/Memory, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Financing education</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>To what extent do you agree or disagree with the following statements? I am worried about my ability to pay for school. I am worried about my ability to repay my student loans in the future [if loans selected above] My student loans negatively impact my mental health [if loans selected above]</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Likert (6-point)</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Reading, Response Categories, Sensitivity/Bias</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2880,7 +3830,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
+          <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -2942,7 +3892,7 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>To what extent to which you agree or disagree with each of the following statements: I feel like sports betting controls my life I have no problem setting limits on how much money I bet on sports</t>
+          <t>To what extent to which you agree or disagree with each of the following statements:I feel like sports betting controls my life. I have no problem setting limits on how much money I bet on sports.</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -2957,7 +3907,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Neither agree nor disagree 5=Somewhat disagree 6=Disagree 7=Strongly disagree</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -3136,7 +4086,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
@@ -3216,7 +4166,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
@@ -3448,7 +4398,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr"/>
@@ -3524,7 +4474,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
@@ -3600,7 +4550,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
@@ -3748,7 +4698,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5067,7 +6017,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7369,7 +8319,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -11,10 +11,9 @@
     <sheet name="Overview" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Overall Health" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Financial Stress" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Academic Persistence, Retention" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Mental Health Status" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Mental Health Service Utilizati" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Academic Persistence, Retention" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Mental Health Status" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Mental Health Service Utilizati" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -696,7 +695,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -708,7 +707,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -723,7 +722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -848,546 +847,491 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Scholarship Status</t>
+          <t xml:space="preserve">  ↳ Spending</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Housing concerns</t>
+          <t xml:space="preserve">  ↳ Scholarship Status</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Financing education</t>
+          <t xml:space="preserve">  ↳ Housing concerns</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0.6</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Socioeconomic status</t>
+          <t xml:space="preserve">  ↳ Financing education</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sheet1</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="n">
+        <v>1.44</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Spending</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>0.09</v>
-      </c>
+          <t>Academic Persistence, Retention</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Scholarship Status</t>
+          <t xml:space="preserve">  ↳ Faculty Advising (Ph D Students)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Housing concerns</t>
+          <t xml:space="preserve">  ↳ Overall social experience</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Financing education</t>
+          <t xml:space="preserve">  ↳ Imposter Syndrome</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0.6</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Socioeconomic status</t>
+          <t xml:space="preserve">  ↳ Clarifying achievement goals and their impact</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>1.44</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Academic Persistence, Retention</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>4.97</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Stress mindset</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="n">
+        <v>0.45</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Faculty Advising (Ph D Students)</t>
+          <t xml:space="preserve">  ↳ Experiences with faculty and academic support services</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Overall social experience</t>
+          <t xml:space="preserve">  ↳ Perceived competition</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0.36</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Imposter Syndrome</t>
+          <t xml:space="preserve">  ↳ Issues affecting academic performance</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.36</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Clarifying achievement goals and their impact</t>
+          <t xml:space="preserve">  ↳ Overall academic experience</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>0.38</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Stress mindset</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="n">
-        <v>0.45</v>
-      </c>
+          <t>Mental Health Status</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Experiences with faculty and academic support services</t>
+          <t xml:space="preserve">  ↳ Eating and body image</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Perceived competition</t>
+          <t xml:space="preserve">  ↳ Psychosis Screen</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Issues affecting academic performance</t>
+          <t xml:space="preserve">  ↳ Loneliness</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.7</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Overall academic experience</t>
+          <t xml:space="preserve">  ↳ Social media/internet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>1.46</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mental Health Status</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Sleep</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="n">
+        <v>0.37</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Eating and body image</t>
+          <t xml:space="preserve">  ↳ Anxiety (GAD-7)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="n">
-        <v>0.09</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Psychosis Screen</t>
+          <t xml:space="preserve">  ↳ Suicide Contagion</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.19</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Loneliness</t>
+          <t xml:space="preserve">  ↳ SDE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.28</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Social media/internet</t>
+          <t xml:space="preserve">  ↳ Substance use</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Sleep</t>
+          <t xml:space="preserve">  ↳ Positive mental health</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Anxiety (GAD-7)</t>
+          <t xml:space="preserve">  ↳ Academic Impairment</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Suicide Contagion</t>
+          <t xml:space="preserve">  ↳ Non-suicidal self-injury</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SDE</t>
+          <t xml:space="preserve">  ↳ Exercise</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.4</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Substance use</t>
+          <t xml:space="preserve">  ↳ Suicidality</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0.4</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Positive mental health</t>
+          <t xml:space="preserve">  ↳ Depression (PHQ-9)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0.41</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Academic Impairment</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="n">
-        <v>0.46</v>
-      </c>
+          <t>Mental Health Service Utilizati</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Non-suicidal self-injury</t>
+          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Exercise</t>
+          <t xml:space="preserve">  ↳ Insurance</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0.52</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Suicidality</t>
+          <t xml:space="preserve">  ↳ Disability</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="n">
-        <v>0.88</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Depression (PHQ-9)</t>
+          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>1.1</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mental Health Service Utilizati</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="n">
+        <v>0.34</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Insurance</t>
+          <t xml:space="preserve">  ↳ Diagnosed mental illnesses</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Disability</t>
+          <t xml:space="preserve">  ↳ Use of medication</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0.28</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Stigma</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.28</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
+          <t xml:space="preserve">  ↳ Perceived need</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.34</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
+          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0.39</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Diagnosed mental illnesses</t>
+          <t xml:space="preserve">  ↳ Informal help-seeking</t>
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.52</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ Use of medication</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="n">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ Stigma</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="n">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ Perceived need</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
-      <c r="C58" t="n">
-        <v>0.66</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="n">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ Informal help-seeking</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr"/>
-      <c r="C60" t="n">
         <v>1.66</v>
       </c>
     </row>
@@ -2710,900 +2654,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
-    <col width="40" customWidth="1" min="20" max="20"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Delivery Order</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Source Question #</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Skip Group ID</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Question Role</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Parent Question #</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Response Type</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Flesch Reading Ease</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>FRE Band</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Blooms Score</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Response Option Complexity</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>Response Option Complexity Score</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>Time-span and Sensitivity</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>QAS problems</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>Cognitive Load Score</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>Cognitive Load Band</t>
-        </is>
-      </c>
-      <c r="S1" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="T1" s="4" t="inlineStr">
-        <is>
-          <t>Skip/Display Logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>6</v>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>Housing concerns</t>
-        </is>
-      </c>
-      <c r="D2" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
-        <is>
-          <t>Do you have any concerns about your current living situation, like housing conditions, safety, and costs?</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr"/>
-      <c r="H2" s="6" t="inlineStr">
-        <is>
-          <t>1=Yes 2=No</t>
-        </is>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="J2" s="6" t="n">
-        <v>50.35</v>
-      </c>
-      <c r="K2" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M2" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N2" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S2" s="6" t="inlineStr"/>
-      <c r="T2" s="6" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Housing concerns</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>What are those concerns? (Select all that apply.</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H3" s="7" t="inlineStr">
-        <is>
-          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J3" s="7" t="inlineStr"/>
-      <c r="K3" s="7" t="inlineStr"/>
-      <c r="L3" s="7" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
-      <c r="N3" s="7" t="inlineStr"/>
-      <c r="O3" s="7" t="inlineStr"/>
-      <c r="P3" s="7" t="inlineStr"/>
-      <c r="Q3" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="7" t="inlineStr"/>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
-        </is>
-      </c>
-      <c r="T3" s="7" t="inlineStr">
-        <is>
-          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>How would you describe your financial situation right now?</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
-        <is>
-          <t>Likert (5-point)</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q4" s="5" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr">
-        <is>
-          <t>CCMH Standardized Data Set</t>
-        </is>
-      </c>
-      <c r="T4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>How would you describe your financial situation while growing up?</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Likert (5-point)</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>30.02</v>
-      </c>
-      <c r="K5" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L5" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="Q5" s="5" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="R5" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S5" s="5" t="inlineStr">
-        <is>
-          <t>CCMH Standardized Data Set</t>
-        </is>
-      </c>
-      <c r="T5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Housing concerns</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources (please specify)</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>57</v>
-      </c>
-      <c r="K6" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L6" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M6" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="R6" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Scholarship Status</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Do you receive scholarship funding from your institution? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="K7" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L7" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M7" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="R7" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Within the past 12 months the food I bought just didn’t last and I didn’t have money to get more.</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>1=Often true 2=Sometimes true 3=Never true</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J8" s="5" t="n">
-        <v>87.94</v>
-      </c>
-      <c r="K8" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L8" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M8" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O8" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="inlineStr">
-        <is>
-          <t>Clarity, Knowledge/Memory</t>
-        </is>
-      </c>
-      <c r="Q8" s="5" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="R8" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S8" s="5" t="inlineStr"/>
-      <c r="T8" s="5" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Within the past 12 months I worried whether our food would run out before we got money to buy more.</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>1=Often true 2=Sometimes true 3=Never true</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>76.59</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>Clarity, Knowledge/Memory</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Within the past 12 months, which of the following expenses have you had difficulty paying for? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>1=School 2=Food 3=Transportation 4=Childcare 5=Health care 6=Textbooks or course materials 7=Housing 8=None of the above [mutually exclusive]</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>49.47</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Response Categories</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="inlineStr"/>
-      <c r="T10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Financing education</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>To what extent do you agree or disagree with the following statements? I am worried about my ability to pay for school. I am worried about my ability to repay my student loans in the future [if loans selected above] My student loans negatively impact my mental health [if loans selected above]</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Likert (6-point)</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>43.41</v>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L11" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M11" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>Clarity, Reading, Response Categories, Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="inlineStr"/>
-      <c r="T11" s="5" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -4698,7 +3748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6017,7 +5067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8319,7 +7369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -898,7 +898,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Socioeconomic status</t>
+          <t xml:space="preserve">  ↳ Socioeconom ic status</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
+          <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -2942,7 +2942,9 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>To what extent to which you agree or disagree with each of the following statements:I feel like sports betting controls my life. I have no problem setting limits on how much money I bet on sports.</t>
+          <t>To what extent to which you agree or disagree with each of the following statements:
+1. I feel like sports betting controls my life.
+2. I have no problem setting limits on how much money I bet on sports.</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -2957,7 +2959,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Neither agree nor disagree 5=Somewhat disagree 6=Disagree 7=Strongly disagree</t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -3136,7 +3138,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
@@ -3216,7 +3218,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
@@ -3448,7 +3450,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr"/>
@@ -3524,7 +3526,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
@@ -3600,7 +3602,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
@@ -8727,12 +8729,12 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8975,12 +8977,12 @@
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="C11" t="inlineStr"/>
     </row>
@@ -870,7 +870,7 @@
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="14">
@@ -881,7 +881,7 @@
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="15">
@@ -913,7 +913,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.97</v>
+        <v>4.98</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.7</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="27">
@@ -1199,7 +1199,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6.74</v>
+        <v>6.72</v>
       </c>
       <c r="C43" t="inlineStr"/>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
     </row>
   </sheetData>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Other (text)</t>
+          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Others</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Other</t>
+          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Others</t>
         </is>
       </c>
       <c r="I7" s="7" t="inlineStr">
@@ -1996,11 +1996,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="S8" s="6" t="inlineStr">
-        <is>
-          <t>help to remember times you went to the hospital or</t>
-        </is>
-      </c>
+      <c r="S8" s="6" t="inlineStr"/>
       <c r="T8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2202,11 +2198,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>help to remember times you went to the hospital or</t>
-        </is>
-      </c>
+      <c r="S11" s="6" t="inlineStr"/>
       <c r="T11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
@@ -2461,7 +2453,7 @@
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>1=I exercise more now. 2=I exercise less now. 3=Other (please specify)</t>
+          <t>1=I exercise more now. 2=I exercise less now. 3=Others</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
@@ -2517,7 +2509,7 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder (please specify) 13=Other chronic disease (please specify) 14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
+          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder  13=Other chronic disease  14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -2526,7 +2518,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>23.49</v>
+        <v>25.16</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -2557,7 +2549,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>0.32</v>
+        <v>0.316</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -2880,7 +2872,7 @@
       </c>
       <c r="E3" s="7" t="inlineStr">
         <is>
-          <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
+          <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
         </is>
       </c>
       <c r="F3" s="7" t="inlineStr">
@@ -3084,7 +3076,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>What are those concerns? (Select all that apply.</t>
+          <t>What are those concerns? (Select all that apply)</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -3099,7 +3091,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Other (please specify)</t>
+          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Others</t>
         </is>
       </c>
       <c r="I6" s="7" t="inlineStr">
@@ -3214,17 +3206,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Housing concerns</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>How would you describe your financial situation while growing up?</t>
+          <t>Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -3235,25 +3227,25 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
+          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Likert (5-point)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>30.02</v>
+        <v>59.75</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="M8" s="5" t="inlineStr">
@@ -3271,22 +3263,18 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Response Categories</t>
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>0.165</v>
+        <v>0.164</v>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S8" s="5" t="inlineStr">
-        <is>
-          <t>CCMH Standardized Data Set</t>
-        </is>
-      </c>
+      <c r="S8" s="5" t="inlineStr"/>
       <c r="T8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
@@ -3294,17 +3282,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Housing concerns</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
+          <t>How would you describe your financial situation while growing up?</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
@@ -3315,25 +3303,25 @@
       <c r="G9" s="5" t="inlineStr"/>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources (please specify)</t>
+          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Likert (5-point)</t>
         </is>
       </c>
       <c r="J9" s="5" t="n">
-        <v>57</v>
+        <v>30.02</v>
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L9" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M9" s="5" t="inlineStr">
@@ -3351,18 +3339,22 @@
       </c>
       <c r="P9" s="5" t="inlineStr">
         <is>
-          <t>Response Categories</t>
+          <t>None</t>
         </is>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>0.169</v>
+        <v>0.165</v>
       </c>
       <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="S9" s="5" t="inlineStr"/>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>CCMH Standardized Data Set</t>
+        </is>
+      </c>
       <c r="T9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
@@ -3391,7 +3383,7 @@
       <c r="G10" s="5" t="inlineStr"/>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other (please specify)</t>
+          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Others</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
@@ -3400,7 +3392,7 @@
         </is>
       </c>
       <c r="J10" s="5" t="n">
-        <v>31.88</v>
+        <v>34.87</v>
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
@@ -3431,7 +3423,7 @@
         </is>
       </c>
       <c r="Q10" s="5" t="n">
-        <v>0.22</v>
+        <v>0.214</v>
       </c>
       <c r="R10" s="5" t="inlineStr">
         <is>
@@ -3909,7 +3901,7 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree (please specify) 6=Don’t know</t>
+          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree  6=Don’t know</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -3918,7 +3910,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>63.98</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
@@ -3949,7 +3941,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
@@ -4036,164 +4028,164 @@
       <c r="T3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Faculty Advising (Ph D Students)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Which best describes how your mental and emotional health is affected by your faculty advisor(s)?</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>PhD Advising Question</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>1=Strong negative effect 2=Somewhat negative effect 3=No effect/neutral effect 4=Somewhat positive effect 5=Strong positive effect</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="n">
+        <v>24.29</v>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Sensitivity/Bias</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Overall academic experience</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Which of the following challenges are most likely to prevent you from finishing your degree? (Select all that apply)</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Independent Question</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>1=Financial challenges 2=Mental or emotional health problems 3=Other health problems (not directly related to mental or emotional health) 4=Family obligations 5=Family or relationship difficulties 6=Academic challenges (struggling to pass classes) 7=[if not U.S. citizen, ask→Visa or other challenges related to being a non-U.S. citizen] 8=Lack of motivation or desire 9=Work or professional commitments 10=Career opportunities 11=Other challenge(s) (please specify)</t>
-        </is>
-      </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>1=Financial challenges 2=Mental or emotional health problems 3=Other health problems (not directly related to mental or emotional health) 4=Family obligations 5=Family or relationship difficulties 6=Academic challenges (struggling to pass classes) 7=Lack of motivation or desire 8=Work or professional commitments 9=Career opportunities 10=Others</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J4" s="5" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="J5" s="5" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N4" s="5" t="n">
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>Response Categories</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="n">
-        <v>0.219</v>
-      </c>
-      <c r="R4" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S4" s="5" t="inlineStr"/>
-      <c r="T4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="n">
-        <v>13</v>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Faculty Advising (Ph D Students)</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Which best describes how your mental and emotional health is affected by your faculty advisor(s)?</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>PhD Advising Question</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>1=Strong negative effect 2=Somewhat negative effect 3=No effect/neutral effect 4=Somewhat positive effect 5=Strong positive effect</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="n">
-        <v>24.29</v>
-      </c>
-      <c r="K5" s="8" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P5" s="8" t="inlineStr">
-        <is>
-          <t>Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="Q5" s="8" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
-        </is>
-      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n">
@@ -5010,7 +5002,7 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>1=I did not experience this. 2=I experienced this but it did not affect my academic performance. 3=I received a lower grade on one or more exams or projects. 4=I received a lower grade in one or more courses. 5=I received an incomplete or dropped one or more courses. 6=I had a significant disruption in research, practicum, thesis, or dissertation work. 7=Other (please specify)</t>
+          <t>1=I did not experience this. 2=I experienced this but it did not affect my academic performance. 3=I received a lower grade on one or more exams or projects. 4=I received a lower grade in one or more courses. 5=I received an incomplete or dropped one or more courses. 6=I had a significant disruption in research, practicum, thesis, or dissertation work. 7=Others</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -5019,7 +5011,7 @@
         </is>
       </c>
       <c r="J16" s="5" t="n">
-        <v>18.68</v>
+        <v>19.51</v>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
@@ -5050,7 +5042,7 @@
         </is>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>0.696</v>
+        <v>0.694</v>
       </c>
       <c r="R16" s="5" t="inlineStr">
         <is>
@@ -6428,7 +6420,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Other (please specify) 7=I don’t remember 8=None of these</t>
+          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember 8=None of these</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -7742,7 +7734,7 @@
       </c>
       <c r="H5" s="7" t="inlineStr">
         <is>
-          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Other (please specify)</t>
+          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Others</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
@@ -8010,7 +8002,7 @@
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Other</t>
+          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Others</t>
         </is>
       </c>
       <c r="I9" s="7" t="inlineStr">
@@ -8057,7 +8049,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? [pipe in selected options from the question, “From which of the following places did you receive counseling or therapy?”]</t>
+          <t xml:space="preserve">Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? </t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -8378,7 +8370,7 @@
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -8460,7 +8452,7 @@
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Others</t>
         </is>
       </c>
       <c r="I16" s="7" t="inlineStr">
@@ -8522,7 +8514,7 @@
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Others</t>
         </is>
       </c>
       <c r="I17" s="7" t="inlineStr">
@@ -8646,7 +8638,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
+          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor  4=Took the medication(s) without a prescription 5=Don’t know</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -8708,7 +8700,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
+          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health  8=None of the above [mutually exclusive]</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -8894,7 +8886,7 @@
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other (please specify)</t>
+          <t xml:space="preserve">1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other </t>
         </is>
       </c>
       <c r="I23" s="7" t="inlineStr">
@@ -9080,7 +9072,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
+          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Others</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">
@@ -9220,7 +9212,7 @@
       <c r="G28" s="5" t="inlineStr"/>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
+          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source 9=No one [mutually exclusive]</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
@@ -9229,7 +9221,7 @@
         </is>
       </c>
       <c r="J28" s="5" t="n">
-        <v>28.36</v>
+        <v>29.91</v>
       </c>
       <c r="K28" s="5" t="inlineStr">
         <is>
@@ -9260,7 +9252,7 @@
         </is>
       </c>
       <c r="Q28" s="5" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="R28" s="5" t="inlineStr">
         <is>
@@ -9275,11 +9267,11 @@
         <v>28</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>Diagnosed mental illnesses</t>
+          <t>Informal help-seeking</t>
         </is>
       </c>
       <c r="D29" s="6" t="n">
@@ -9287,7 +9279,7 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Have you ever been diagnosed with any of the following conditions by a health professional (e.g., primary care doctor, psychiatrist, psychologist, etc.)? (Select all that apply)</t>
+          <t>In the past 12 months have you received support for your mental or emotional health from any of the following sources? (Select all that apply)</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
@@ -9298,7 +9290,7 @@
       <c r="G29" s="6" t="inlineStr"/>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
+          <t>1=Roommate 2=Friend (who is not a roommate) 3=Significant other 4=Family member 5=Religious counselor or other religious contact 6=Support group 9=Faculty member/professor/instructor 10=Staff member 7=Other non-clinical source  8=No, none of these [mutually exclusive]</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
@@ -9307,11 +9299,11 @@
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>0</v>
+        <v>41.97</v>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr">
@@ -9334,11 +9326,11 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>Reading, Response Categories</t>
+          <t>Knowledge/Memory, Response Categories, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q29" s="6" t="n">
-        <v>0.517</v>
+        <v>0.516</v>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -9353,11 +9345,11 @@
         <v>29</v>
       </c>
       <c r="B30" s="7" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Diagnosed mental illnesses</t>
+          <t>Informal help-seeking</t>
         </is>
       </c>
       <c r="D30" s="7" t="n">
@@ -9365,7 +9357,7 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following depressive disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>How helpful was it to discuss these concerns?</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -9375,17 +9367,17 @@
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
         </is>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Categorical (Ordinal)</t>
         </is>
       </c>
       <c r="J30" s="7" t="inlineStr"/>
@@ -9401,95 +9393,111 @@
       <c r="R30" s="7" t="inlineStr"/>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
         </is>
       </c>
       <c r="T30" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="B31" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>Diagnosed mental illnesses</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>Specifically, which of the following bipolar and related disorders were you diagnosed with by a professional? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F31" s="7" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="G31" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H31" s="7" t="inlineStr">
-        <is>
-          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Other (please specify) 5=Don’t know</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="inlineStr">
+      <c r="D31" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>Have you ever been diagnosed with any of the following conditions by a health professional (e.g., primary care doctor, psychiatrist, psychologist, etc.)? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J31" s="7" t="inlineStr"/>
-      <c r="K31" s="7" t="inlineStr"/>
-      <c r="L31" s="7" t="inlineStr"/>
-      <c r="M31" s="7" t="inlineStr"/>
-      <c r="N31" s="7" t="inlineStr"/>
-      <c r="O31" s="7" t="inlineStr"/>
-      <c r="P31" s="7" t="inlineStr"/>
-      <c r="Q31" s="7" t="n">
+      <c r="J31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R31" s="7" t="inlineStr"/>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
-        </is>
-      </c>
-      <c r="T31" s="7" t="inlineStr">
-        <is>
-          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
-        </is>
-      </c>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L31" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Reading, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr"/>
+      <c r="T31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>Diagnosed mental illnesses</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="C32" s="7" t="inlineStr">
-        <is>
-          <t>Diagnosed mental illnesses</t>
-        </is>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>3</v>
-      </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following anxiety disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following depressive disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -9504,7 +9512,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -9525,12 +9533,12 @@
       <c r="R32" s="7" t="inlineStr"/>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T32" s="7" t="inlineStr">
         <is>
-          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "1=Depression" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9547,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
@@ -9547,11 +9555,11 @@
         </is>
       </c>
       <c r="D33" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following obsessive-compulsive or related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following bipolar and related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -9566,7 +9574,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -9587,12 +9595,12 @@
       <c r="R33" s="7" t="inlineStr"/>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T33" s="7" t="inlineStr">
         <is>
-          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "2=Bipolar" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9601,7 +9609,7 @@
         <v>33</v>
       </c>
       <c r="B34" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
@@ -9609,11 +9617,11 @@
         </is>
       </c>
       <c r="D34" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following trauma and stressor related disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following anxiety disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -9628,7 +9636,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Others  7=Don’t know</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -9649,12 +9657,12 @@
       <c r="R34" s="7" t="inlineStr"/>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T34" s="7" t="inlineStr">
         <is>
-          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "3=Anxiety" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9671,7 @@
         <v>34</v>
       </c>
       <c r="B35" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
@@ -9671,11 +9679,11 @@
         </is>
       </c>
       <c r="D35" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following obsessive-compulsive or related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -9690,7 +9698,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Others 7=Don’t know</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -9711,12 +9719,12 @@
       <c r="R35" s="7" t="inlineStr"/>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T35" s="7" t="inlineStr">
         <is>
-          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "4=Obsessive-compulsive or related disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9725,7 +9733,7 @@
         <v>35</v>
       </c>
       <c r="B36" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
@@ -9733,11 +9741,11 @@
         </is>
       </c>
       <c r="D36" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following eating disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following trauma and stressor related disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -9752,7 +9760,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -9773,12 +9781,12 @@
       <c r="R36" s="7" t="inlineStr"/>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T36" s="7" t="inlineStr">
         <is>
-          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "5=Trauma and Stressor Related Disorders" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9795,7 @@
         <v>36</v>
       </c>
       <c r="B37" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
@@ -9795,11 +9803,11 @@
         </is>
       </c>
       <c r="D37" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following psychotic disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -9814,7 +9822,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -9835,12 +9843,12 @@
       <c r="R37" s="7" t="inlineStr"/>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T37" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "6=Neurodevelopmental disorder or intellectual disability" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9857,7 @@
         <v>37</v>
       </c>
       <c r="B38" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
@@ -9857,11 +9865,11 @@
         </is>
       </c>
       <c r="D38" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following personality disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following eating disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -9876,7 +9884,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Other (please specify) 12=Don’t know</t>
+          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Others 7=Don’t know</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -9897,12 +9905,12 @@
       <c r="R38" s="7" t="inlineStr"/>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T38" s="7" t="inlineStr">
         <is>
-          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "7=Eating disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9919,7 @@
         <v>38</v>
       </c>
       <c r="B39" s="7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
@@ -9919,11 +9927,11 @@
         </is>
       </c>
       <c r="D39" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>Specifically, which of the following substance disorders were you diagnosed with by a professional? (Select all that apply)</t>
+          <t>Specifically, which of the following psychotic disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -9938,7 +9946,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Other (please specify) 3=Don’t know</t>
+          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Others  7=Don’t know</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -9959,111 +9967,95 @@
       <c r="R39" s="7" t="inlineStr"/>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T39" s="7" t="inlineStr">
         <is>
-          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+          <t>Display if "8=Psychosis" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="n">
+      <c r="A40" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>Disability</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>Do you have a disability or disabilities from any of the following categories? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6" t="inlineStr">
-        <is>
-          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Other (please specify) 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
+      <c r="B40" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Diagnosed mental illnesses</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Specifically, which of the following personality disorders were you diagnosed with by a professional? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Others 12=Don’t know</t>
+        </is>
+      </c>
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="7" t="inlineStr"/>
+      <c r="K40" s="7" t="inlineStr"/>
+      <c r="L40" s="7" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+      <c r="N40" s="7" t="inlineStr"/>
+      <c r="O40" s="7" t="inlineStr"/>
+      <c r="P40" s="7" t="inlineStr"/>
+      <c r="Q40" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="L40" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M40" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N40" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S40" s="6" t="inlineStr"/>
-      <c r="T40" s="6" t="inlineStr"/>
+      <c r="R40" s="7" t="inlineStr"/>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+        </is>
+      </c>
+      <c r="T40" s="7" t="inlineStr">
+        <is>
+          <t>Display if "9=Personality disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>Disability</t>
+          <t>Diagnosed mental illnesses</t>
         </is>
       </c>
       <c r="D41" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>Are you registered with the office for disability services/ADA office on this campus as having a disability?</t>
+          <t>Specifically, which of the following substance disorders were you diagnosed with by a professional? (Select all that apply)</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -10073,12 +10065,12 @@
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>1=Yes 2=No 3=Prefer not to say</t>
+          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Others  3=Don’t know</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">
@@ -10099,83 +10091,99 @@
       <c r="R41" s="7" t="inlineStr"/>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
       <c r="T41" s="7" t="inlineStr">
         <is>
-          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if "10=Substance use disorder" is selected for "Have you ever been diagnosed with any of the following conditions by a health professional"</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="n">
+      <c r="A42" s="6" t="n">
         <v>41</v>
       </c>
-      <c r="B42" s="7" t="n">
-        <v>14</v>
-      </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="B42" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>Disability</t>
         </is>
       </c>
-      <c r="D42" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E42" s="7" t="inlineStr">
-        <is>
-          <t>When were you diagnosed with ADHD ?</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>7; 12</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>0=Prior to starting college 1=After starting college</t>
-        </is>
-      </c>
-      <c r="I42" s="7" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="J42" s="7" t="inlineStr"/>
-      <c r="K42" s="7" t="inlineStr"/>
-      <c r="L42" s="7" t="inlineStr"/>
-      <c r="M42" s="7" t="inlineStr"/>
-      <c r="N42" s="7" t="inlineStr"/>
-      <c r="O42" s="7" t="inlineStr"/>
-      <c r="P42" s="7" t="inlineStr"/>
-      <c r="Q42" s="7" t="n">
+      <c r="D42" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>Do you have a disability or disabilities from any of the following categories? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr"/>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Others 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="R42" s="7" t="inlineStr"/>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
-        </is>
-      </c>
-      <c r="T42" s="7" t="inlineStr">
-        <is>
-          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
-        </is>
-      </c>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S42" s="6" t="inlineStr"/>
+      <c r="T42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C43" s="7" t="inlineStr">
         <is>
@@ -10183,11 +10191,11 @@
         </is>
       </c>
       <c r="D43" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>What type of treatment for ADHD have you received in the past year?</t>
+          <t>Are you registered with the office for disability services/ADA office on this campus as having a disability?</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -10197,12 +10205,12 @@
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Other (please specify)</t>
+          <t>1=Yes 2=No 3=Prefer not to say</t>
         </is>
       </c>
       <c r="I43" s="7" t="inlineStr">
@@ -10223,12 +10231,12 @@
       <c r="R43" s="7" t="inlineStr"/>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>Display if previous question is displayed</t>
+          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
       <c r="T43" s="7" t="inlineStr">
         <is>
-          <t>Display if previous question is displayed</t>
+          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
     </row>
@@ -10237,7 +10245,7 @@
         <v>43</v>
       </c>
       <c r="B44" s="7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
@@ -10245,11 +10253,11 @@
         </is>
       </c>
       <c r="D44" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>What type of treatment for ADHD did you receive prior to starting college?</t>
+          <t>When were you diagnosed with ADHD ?</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -10259,17 +10267,17 @@
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>7; 12</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Other (please specify)</t>
+          <t>0=Prior to starting college 1=After starting college</t>
         </is>
       </c>
       <c r="I44" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Nominal)</t>
+          <t>Boolean</t>
         </is>
       </c>
       <c r="J44" s="7" t="inlineStr"/>
@@ -10285,12 +10293,12 @@
       <c r="R44" s="7" t="inlineStr"/>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
+          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
         </is>
       </c>
       <c r="T44" s="7" t="inlineStr">
         <is>
-          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
+          <t>Display if “1=ADHD” is selected for “Specifically, which of the following neurodevelopmental disorders or intellectual disabilities were you diagnosed with by a professional?” or “1=Attention deficit/hyperactivity disorders” is selected for “Do you have a disability or disabilities from any of the following categories?”</t>
         </is>
       </c>
     </row>
@@ -10299,19 +10307,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="7" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="C45" s="7" t="inlineStr">
         <is>
-          <t>Use of medication</t>
+          <t>Disability</t>
         </is>
       </c>
       <c r="D45" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>Within the last 12 months, how has ADHD affected your academic performance?</t>
+          <t>What type of treatment for ADHD have you received in the past year?</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -10321,12 +10329,12 @@
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>7; 12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>1=It has not impaired my academic performance 2=It has minimally impaired my academic performance 3=It has moderately impaired my academic performance 4=It has significantly impaired my academic performance</t>
+          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Others</t>
         </is>
       </c>
       <c r="I45" s="7" t="inlineStr">
@@ -10347,103 +10355,87 @@
       <c r="R45" s="7" t="inlineStr"/>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if previous question is displayed</t>
         </is>
       </c>
       <c r="T45" s="7" t="inlineStr">
         <is>
-          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if previous question is displayed</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="n">
+      <c r="A46" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="B46" s="6" t="n">
-        <v>46</v>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Informal help-seeking</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="n">
+      <c r="B46" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Disability</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>In the past 12 months have you received support for your mental or emotional health from any of the following sources? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>1=Roommate 2=Friend (who is not a roommate) 3=Significant other 4=Family member 5=Religious counselor or other religious contact 6=Support group 9=Faculty member/professor/instructor 10=Staff member 7=Other non-clinical source (please specify) 8=No, none of these [mutually exclusive]</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>What type of treatment for ADHD did you receive prior to starting college?</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Others</t>
+        </is>
+      </c>
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J46" s="6" t="n">
-        <v>40.1</v>
-      </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L46" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M46" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N46" s="6" t="n">
+      <c r="J46" s="7" t="inlineStr"/>
+      <c r="K46" s="7" t="inlineStr"/>
+      <c r="L46" s="7" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+      <c r="N46" s="7" t="inlineStr"/>
+      <c r="O46" s="7" t="inlineStr"/>
+      <c r="P46" s="7" t="inlineStr"/>
+      <c r="Q46" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="O46" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Response Categories, Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S46" s="6" t="inlineStr"/>
-      <c r="T46" s="6" t="inlineStr"/>
+      <c r="R46" s="7" t="inlineStr"/>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
+        </is>
+      </c>
+      <c r="T46" s="7" t="inlineStr">
+        <is>
+          <t>Display if “0=Prior to starting college” is selected for “When were you diagnosed with ADHD ?”</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="7" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C47" s="7" t="inlineStr">
         <is>
-          <t>Informal help-seeking</t>
+          <t>Use of medication</t>
         </is>
       </c>
       <c r="D47" s="7" t="n">
@@ -10451,7 +10443,7 @@
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>How helpful was it to discuss these concerns?</t>
+          <t>Within the last 12 months, how has ADHD affected your academic performance?</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -10461,17 +10453,17 @@
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>7; 12</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>1=Very helpful 2=Helpful 3=Somewhat helpful 4=Not helpful</t>
+          <t>1=It has not impaired my academic performance 2=It has minimally impaired my academic performance 3=It has moderately impaired my academic performance 4=It has significantly impaired my academic performance</t>
         </is>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
-          <t>Categorical (Ordinal)</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="J47" s="7" t="inlineStr"/>
@@ -10487,12 +10479,12 @@
       <c r="R47" s="7" t="inlineStr"/>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
       <c r="T47" s="7" t="inlineStr">
         <is>
-          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
     </row>
@@ -10666,7 +10658,7 @@
       <c r="G50" s="5" t="inlineStr"/>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>1=I haven’t had the chance to go but I plan to. 2=No need for services 3=Financial reasons (too expensive, not covered by insurance) 4=Not enough time 5=Not sure where to go 6=Difficulty finding an available appointment 7=Prefer to deal with issues on my own or with support from family/friends 8=Other (please specify) 9=No barriers [mutually exclusive] 10=Privacy concerns 11=People providing services don’t understand me 12=Fear of being mistreated due to my identity/identities 13=The clinic or clinician had limits on the number of times I could be seen</t>
+          <t>1=I haven’t had the chance to go but I plan to. 2=No need for services 3=Financial reasons (too expensive, not covered by insurance) 4=Not enough time 5=Not sure where to go 6=Difficulty finding an available appointment 7=Prefer to deal with issues on my own or with support from family/friends 8=Others  9=No barriers [mutually exclusive] 10=Privacy concerns 11=People providing services don’t understand me 12=Fear of being mistreated due to my identity/identities 13=The clinic or clinician had limits on the number of times I could be seen</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
@@ -10675,7 +10667,7 @@
         </is>
       </c>
       <c r="J50" s="5" t="n">
-        <v>53.89</v>
+        <v>55.18</v>
       </c>
       <c r="K50" s="5" t="inlineStr">
         <is>
@@ -10706,7 +10698,7 @@
         </is>
       </c>
       <c r="Q50" s="5" t="n">
-        <v>0.576</v>
+        <v>0.573</v>
       </c>
       <c r="R50" s="5" t="inlineStr">
         <is>
@@ -10742,7 +10734,7 @@
       <c r="G51" s="5" t="inlineStr"/>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>1=No need for services 2=Financial reasons (too expensive, not covered by insurance) 3=Not enough time 4=Not sure where to go 5=Difficulty finding an available appointment 6=Prefer to deal with issues on my own or with support from family/friends 7=Privacy concerns 8= People providing services don’t understand me 9=Other (please specify) 10= No barriers [mutually exclusive] 11= fear of being mistreated due to my identity/identities 12=The clinic or clinician had limits on the number of times I could be seen</t>
+          <t>1=No need for services 2=Financial reasons (too expensive, not covered by insurance) 3=Not enough time 4=Not sure where to go 5=Difficulty finding an available appointment 6=Prefer to deal with issues on my own or with support from family/friends 7=Privacy concerns 8= People providing services don’t understand me 9=Other 10= No barriers [mutually exclusive] 11= fear of being mistreated due to my identity/identities 12=The clinic or clinician had limits on the number of times I could be seen</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
@@ -10751,7 +10743,7 @@
         </is>
       </c>
       <c r="J51" s="5" t="n">
-        <v>44.62</v>
+        <v>45.8</v>
       </c>
       <c r="K51" s="5" t="inlineStr">
         <is>
@@ -10782,7 +10774,7 @@
         </is>
       </c>
       <c r="Q51" s="5" t="n">
-        <v>0.594</v>
+        <v>0.592</v>
       </c>
       <c r="R51" s="5" t="inlineStr">
         <is>
@@ -10818,7 +10810,7 @@
       <c r="G52" s="5" t="inlineStr"/>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>1=Professor/Instructor from one of my classes 2=Academic advisor/academic counselor 3=Another faculty member or instructor 4=Teaching assistant 5=Student services staff 6=Dean of Students or class dean 7=Other (please specify) 8=No one [mutually exclusive]</t>
+          <t>1=Professor/Instructor from one of my classes 2=Academic advisor/academic counselor 3=Another faculty member or instructor 4=Teaching assistant 5=Student services staff 6=Dean of Students or class dean 7=Others  8=No one [mutually exclusive]</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
@@ -10827,7 +10819,7 @@
         </is>
       </c>
       <c r="J52" s="5" t="n">
-        <v>40.19</v>
+        <v>42.15</v>
       </c>
       <c r="K52" s="5" t="inlineStr">
         <is>
@@ -10858,11 +10850,11 @@
         </is>
       </c>
       <c r="Q52" s="5" t="n">
-        <v>0.603</v>
+        <v>0.599</v>
       </c>
       <c r="R52" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S52" s="5" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -8710,12 +8710,12 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8958,12 +8958,12 @@
       <c r="R24" s="7" t="inlineStr"/>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="T24" s="7" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -7513,7 +7513,7 @@
       <c r="G2" s="6" t="inlineStr"/>
       <c r="H2" s="6" t="inlineStr">
         <is>
-          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have health insurance through an embassy or sponsoring agency for international students. 7=I have individual health insurance purchased directly from an insurance carrier. 8=I have Medicaid or other governmental insurance. 9=I am uncertain about whether I have health insurance. 10=I have health insurance but am uncertain about where it is from.</t>
+          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have individual health insurance purchased directly from an insurance carrier. 7=I have a governmental insurance plan. 8=I am uncertain about whether I have health insurance.[mutually exclusive] 9=I have health insurance but am uncertain about where it is from.[mutually exclusive]</t>
         </is>
       </c>
       <c r="I2" s="6" t="inlineStr">
@@ -7522,7 +7522,7 @@
         </is>
       </c>
       <c r="J2" s="6" t="n">
-        <v>33.45</v>
+        <v>33.82</v>
       </c>
       <c r="K2" s="6" t="inlineStr">
         <is>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -9046,7 +9046,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
+          <t>Which of the following are important reasons why you received the counselling services? (Select all that apply)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -887,7 +887,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Socioeconom ic status</t>
+          <t xml:space="preserve">  ↳ Socioeconomic status</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr"/>
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr"/>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
@@ -3583,7 +3583,7 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -4091,12 +4091,12 @@
       </c>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
+          <t>Display if "MS by Research scholar" or "PhD Scholar" is selected for "What is your role at IIITB?" (Faculty Advising is a PhD/research-degree program dependency -- references the Demographics Role question, not a question in this module.</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
+          <t>Display if "MS by Research scholar" or "PhD Scholar" is selected for "What is your role at IIITB?" (Faculty Advising is a PhD/research-degree program dependency -- references the Demographics Role question, not a question in this module.</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4.98</v>
+        <v>5.15</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -920,7 +920,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Overall social experience</t>
+          <t xml:space="preserve">  ↳ Imposter Syndrome</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -931,23 +931,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Imposter Syndrome</t>
+          <t xml:space="preserve">  ↳ Clarifying achievement goals and their impact</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Clarifying achievement goals and their impact</t>
+          <t xml:space="preserve">  ↳ Overall social experience</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="22">
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="25">
@@ -4181,17 +4181,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>Perceived competition</t>
+          <t>Overall academic experience</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr"/>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>How frequently do instructors in your major/field of study grade your work on a curve (adjust grades based on the grade distribution among students in a class)?</t>
+          <t>How has it been to adjust to the academic demands of college since you began as a student at your school?</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -4202,16 +4202,16 @@
       <c r="G6" s="5" t="inlineStr"/>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>1=Never 2=Almost never 3=Occasionally/sometimes 4=Almost every time 5=Every time</t>
+          <t>1=Very easy 2=Easy 3=Somewhat easy 4=Somewhat difficult 5=Difficult 6=Very difficult</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Categorical (Ordinal)</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J6" s="5" t="n">
-        <v>40.11</v>
+        <v>49.51</v>
       </c>
       <c r="K6" s="5" t="inlineStr">
         <is>
@@ -4225,11 +4225,11 @@
       </c>
       <c r="M6" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.299</v>
+        <v>0</v>
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
@@ -4238,11 +4238,11 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Assumptions, Knowledge/Memory</t>
         </is>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>0.253</v>
+        <v>0.268</v>
       </c>
       <c r="R6" s="5" t="inlineStr">
         <is>
@@ -4257,17 +4257,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Overall academic experience</t>
+          <t>Perceived competition</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr"/>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>How has it been to adjust to the academic demands of [college/graduate school] since you began as a student at your school?</t>
+          <t>How would you rate the overall competitiveness among students… …in your current classes? …at your school? …in your field of study?</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -4278,20 +4278,20 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>1=Very easy 2=Easy 3=Somewhat easy 4=Somewhat difficult 5=Difficult 6=Very difficult</t>
+          <t>1=Very competitive 2=Competitive 3=Somewhat competitive 4=Not competitive 5=Very uncompetitive</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J7" s="5" t="n">
-        <v>48.23</v>
+        <v>11.27</v>
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L7" s="5" t="inlineStr">
@@ -4301,11 +4301,11 @@
       </c>
       <c r="M7" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
@@ -4314,18 +4314,22 @@
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>Assumptions, Knowledge/Memory</t>
+          <t>Response Categories</t>
         </is>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>0.27</v>
+        <v>0.311</v>
       </c>
       <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr"/>
+      <c r="S7" s="5" t="inlineStr">
+        <is>
+          <t>Matrix table with 3 questions.</t>
+        </is>
+      </c>
       <c r="T7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
@@ -4333,17 +4337,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Perceived competition</t>
+          <t>Overall academic experience</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>How would you rate the overall competitiveness among students… …in your current classes? …at your school? …in your field of study?</t>
+          <t>Have you… …decided to pursue a different major since you began as a student at your school? …failed one or more courses since you began as a student at your school?</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -4354,7 +4358,7 @@
       <c r="G8" s="5" t="inlineStr"/>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>1=Very competitive 2=Competitive 3=Somewhat competitive 4=Not competitive 5=Very uncompetitive</t>
+          <t>1=Yes 0=No</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
@@ -4363,11 +4367,11 @@
         </is>
       </c>
       <c r="J8" s="5" t="n">
-        <v>11.27</v>
+        <v>70.28</v>
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -4390,11 +4394,11 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>Response Categories</t>
+          <t>Assumptions, Knowledge/Memory, Reading</t>
         </is>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>0.311</v>
+        <v>0.359</v>
       </c>
       <c r="R8" s="5" t="inlineStr">
         <is>
@@ -4403,7 +4407,7 @@
       </c>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>Matrix table with 3 questions.</t>
+          <t>Matrix table with 2 questions.</t>
         </is>
       </c>
       <c r="T8" s="5" t="inlineStr"/>
@@ -4413,171 +4417,15 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Overall social experience</t>
+          <t>Imposter Syndrome</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr"/>
       <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>How has it been to… …develop close friendships with other students at your school? …manage your time effectively since you began as a student at your school?</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>1=Very easy 2=Easy 3=Somewhat easy 4=Somewhat difficult 5=Difficult 6=Very difficult</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Likert (6-point)</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>46.66</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L9" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M9" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>Assumptions, Knowledge/Memory, Reading</t>
-        </is>
-      </c>
-      <c r="Q9" s="5" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="R9" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Overall academic experience</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>Have you… …decided to pursue a different major since you began as a student at your school? …failed one or more courses since you began as a student at your school?</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>1=Yes 0=No</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Matrix</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="n">
-        <v>70.28</v>
-      </c>
-      <c r="K10" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L10" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M10" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O10" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="inlineStr">
-        <is>
-          <t>Assumptions, Knowledge/Memory, Reading</t>
-        </is>
-      </c>
-      <c r="Q10" s="5" t="n">
-        <v>0.359</v>
-      </c>
-      <c r="R10" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S10" s="5" t="inlineStr">
-        <is>
-          <t>Matrix table with 2 questions.</t>
-        </is>
-      </c>
-      <c r="T10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Imposter Syndrome</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>How much do you agree with the following statements?
 1. I’m afraid people important to me may find out that I’m not as capable as they think I am.
@@ -4587,6 +4435,162 @@
 5. I often compare my ability to those around me and think they may be more intelligent than I am.</t>
         </is>
       </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>1=Strongly disagree 2=Disagree 3=Neither agree nor disagree 4=Agree 5=Strongly agree</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Matrix</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>67.51000000000001</v>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Reading, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q9" s="5" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="R9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S9" s="5" t="inlineStr">
+        <is>
+          <t>Matrix table with 5 statements. Adapted from The Imposter Phenomenon (Clance, 1985)</t>
+        </is>
+      </c>
+      <c r="T9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Perceived competition</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">How often do professors or external examiners in your course/department use relative grading (scaling or adjusting marks based on the overall performance of the class rather than using fixed passing marks)? </t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>1=Never 2=Almost never 3=Occasionally/sometimes 4=Almost every time 5=Every time</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Reading</t>
+        </is>
+      </c>
+      <c r="Q10" s="5" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="R10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="S10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Overall academic experience</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>How much do you agree with the following statements? I have doubts about whether higher education is worth the time, money, and effort that I’m spending on it. My family is very supportive of my educational goals. My professors believe in my potential to succeed academically.</t>
+        </is>
+      </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
           <t>Independent Question</t>
@@ -4595,20 +4599,20 @@
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>1=Strongly disagree 2=Disagree 3=Neither agree nor disagree 4=Agree 5=Strongly agree</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Matrix</t>
+          <t>Likert (6-point)</t>
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>67.51000000000001</v>
+        <v>37.79</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -4618,35 +4622,31 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Reading, Response Categories</t>
+        </is>
+      </c>
+      <c r="Q11" s="5" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="R11" s="5" t="inlineStr">
+        <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="N11" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O11" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P11" s="5" t="inlineStr">
-        <is>
-          <t>Clarity, Reading, Response Categories</t>
-        </is>
-      </c>
-      <c r="Q11" s="5" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="R11" s="5" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S11" s="5" t="inlineStr">
-        <is>
-          <t>Matrix table with 5 statements. Adapted from The Imposter Phenomenon (Clance, 1985)</t>
-        </is>
-      </c>
+      <c r="S11" s="5" t="inlineStr"/>
       <c r="T11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4654,17 +4654,17 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Overall academic experience</t>
+          <t>Clarifying achievement goals and their impact</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>How much do you agree with the following statements? I have doubts about whether higher education is worth the time, money, and effort that I’m spending on it. My family is very supportive of my educational goals. My professors believe in my potential to succeed academically.</t>
+          <t>How much do you agree with the following statements? It is very important to me to do well in my courses. It is important to me to confirm my intelligence through my schoolwork. In school, I am always seeking opportunities to develop new skills and acquire new knowledge. It is very important to me to feel that my coursework offers me real challenges.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4675,20 +4675,20 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+          <t>1=Strongly disagree 2=Disagree 3=Neither agree nor disagree 4=Agree 5=Strongly agree</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>37.79</v>
+        <v>58.04</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -4698,11 +4698,11 @@
       </c>
       <c r="M12" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
@@ -4715,14 +4715,18 @@
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>0.374</v>
+        <v>0.384</v>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S12" s="5" t="inlineStr"/>
+      <c r="S12" s="5" t="inlineStr">
+        <is>
+          <t>Matrix table with 4 statements. Adapted from Achievement Goal Inventory (Grant &amp; Dweck, 2003)</t>
+        </is>
+      </c>
       <c r="T12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
@@ -4730,17 +4734,17 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Clarifying achievement goals and their impact</t>
+          <t>Overall social experience</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>How much do you agree with the following statements? It is very important to me to do well in my courses. It is important to me to confirm my intelligence through my schoolwork. In school, I am always seeking opportunities to develop new skills and acquire new knowledge. It is very important to me to feel that my coursework offers me real challenges.</t>
+          <t>How has it been to… …develop close friendships with other students at your school? …manage your time effectively since you began as a student at your school?</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -4751,7 +4755,7 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>1=Strongly disagree 2=Disagree 3=Neither agree nor disagree 4=Agree 5=Strongly agree</t>
+          <t>1=Very easy 2=Easy 3=Somewhat easy 4=Somewhat difficult 5=Difficult 6=Very difficult</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -4760,7 +4764,7 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>58.04</v>
+        <v>46.66</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
@@ -4787,11 +4791,11 @@
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>Clarity, Reading, Response Categories</t>
+          <t>Assumptions, Knowledge/Memory, Reading</t>
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>0.384</v>
+        <v>0.407</v>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
@@ -4800,7 +4804,7 @@
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>Matrix table with 4 statements. Adapted from Achievement Goal Inventory (Grant &amp; Dweck, 2003)</t>
+          <t>Matrix table with 2 questions.</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr"/>
@@ -5601,7 +5605,7 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>0=No 1=Yes</t>
+          <t>1=Yes 0=No</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
@@ -8359,7 +8363,7 @@
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -8368,7 +8372,7 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -8399,11 +8403,11 @@
         </is>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.6</v>
+        <v>0.597</v>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr"/>
@@ -8689,7 +8693,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health  8=None of the above [mutually exclusive]</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -854,23 +854,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Scholarship Status</t>
+          <t xml:space="preserve">  ↳ Housing concerns</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="n">
-        <v>0.21</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Housing concerns</t>
+          <t xml:space="preserve">  ↳ Scholarship Status</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="n">
-        <v>0.26</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="15">
@@ -881,7 +881,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0.6</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="16">
@@ -3199,7 +3199,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Housing concerns</t>
+          <t>Financing education</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr"/>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.61</v>
+        <v>2.66</v>
       </c>
       <c r="C11" t="inlineStr"/>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0.76</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J14" s="5" t="n">
@@ -3699,11 +3699,11 @@
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
@@ -3716,14 +3716,18 @@
         </is>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>0.597</v>
+        <v>0.647</v>
       </c>
       <c r="R14" s="5" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="S14" s="5" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="S14" s="5" t="inlineStr">
+        <is>
+          <t>Matrix table with 3 statements.</t>
+        </is>
+      </c>
       <c r="T14" s="5" t="inlineStr"/>
     </row>
   </sheetData>
@@ -5605,7 +5609,7 @@
       <c r="G7" s="5" t="inlineStr"/>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>1=Yes 0=No</t>
+          <t>0=No 1=Yes</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.15</v>
+        <v>5.2</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="27">
@@ -4582,17 +4582,17 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Overall academic experience</t>
+          <t>Clarifying achievement goals and their impact</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr"/>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>How much do you agree with the following statements? I have doubts about whether higher education is worth the time, money, and effort that I’m spending on it. My family is very supportive of my educational goals. My professors believe in my potential to succeed academically.</t>
+          <t>How much do you agree with the following statements? It is very important to me to do well in my courses. It is important to me to confirm my intelligence through my schoolwork. In school, I am always seeking opportunities to develop new skills and acquire new knowledge. It is very important to me to feel that my coursework offers me real challenges.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -4603,20 +4603,20 @@
       <c r="G11" s="5" t="inlineStr"/>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+          <t>1=Strongly disagree 2=Disagree 3=Neither agree nor disagree 4=Agree 5=Strongly agree</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J11" s="5" t="n">
-        <v>37.79</v>
+        <v>58.04</v>
       </c>
       <c r="K11" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="L11" s="5" t="inlineStr">
@@ -4626,11 +4626,11 @@
       </c>
       <c r="M11" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
@@ -4643,14 +4643,18 @@
         </is>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>0.374</v>
+        <v>0.384</v>
       </c>
       <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr"/>
+      <c r="S11" s="5" t="inlineStr">
+        <is>
+          <t>Matrix table with 4 statements. Adapted from Achievement Goal Inventory (Grant &amp; Dweck, 2003)</t>
+        </is>
+      </c>
       <c r="T11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
@@ -4658,17 +4662,17 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Clarifying achievement goals and their impact</t>
+          <t>Overall social experience</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr"/>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>How much do you agree with the following statements? It is very important to me to do well in my courses. It is important to me to confirm my intelligence through my schoolwork. In school, I am always seeking opportunities to develop new skills and acquire new knowledge. It is very important to me to feel that my coursework offers me real challenges.</t>
+          <t>How has it been to… …develop close friendships with other students at your school? …manage your time effectively since you began as a student at your school?</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -4679,7 +4683,7 @@
       <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>1=Strongly disagree 2=Disagree 3=Neither agree nor disagree 4=Agree 5=Strongly agree</t>
+          <t>1=Very easy 2=Easy 3=Somewhat easy 4=Somewhat difficult 5=Difficult 6=Very difficult</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
@@ -4688,7 +4692,7 @@
         </is>
       </c>
       <c r="J12" s="5" t="n">
-        <v>58.04</v>
+        <v>46.66</v>
       </c>
       <c r="K12" s="5" t="inlineStr">
         <is>
@@ -4715,11 +4719,11 @@
       </c>
       <c r="P12" s="5" t="inlineStr">
         <is>
-          <t>Clarity, Reading, Response Categories</t>
+          <t>Assumptions, Knowledge/Memory, Reading</t>
         </is>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>0.384</v>
+        <v>0.407</v>
       </c>
       <c r="R12" s="5" t="inlineStr">
         <is>
@@ -4728,7 +4732,7 @@
       </c>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>Matrix table with 4 statements. Adapted from Achievement Goal Inventory (Grant &amp; Dweck, 2003)</t>
+          <t>Matrix table with 2 questions.</t>
         </is>
       </c>
       <c r="T12" s="5" t="inlineStr"/>
@@ -4738,17 +4742,17 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Overall social experience</t>
+          <t>Overall academic experience</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr"/>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>How has it been to… …develop close friendships with other students at your school? …manage your time effectively since you began as a student at your school?</t>
+          <t>How much do you agree with the following statements? I have doubts about whether higher education is worth the time, money, and effort that I’m spending on it. My family is very supportive of my educational goals. My professors believe in my potential to succeed academically.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -4759,7 +4763,7 @@
       <c r="G13" s="5" t="inlineStr"/>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>1=Very easy 2=Easy 3=Somewhat easy 4=Somewhat difficult 5=Difficult 6=Very difficult</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
@@ -4768,11 +4772,11 @@
         </is>
       </c>
       <c r="J13" s="5" t="n">
-        <v>46.66</v>
+        <v>37.79</v>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L13" s="5" t="inlineStr">
@@ -4795,11 +4799,11 @@
       </c>
       <c r="P13" s="5" t="inlineStr">
         <is>
-          <t>Assumptions, Knowledge/Memory, Reading</t>
+          <t>Clarity, Reading, Response Categories</t>
         </is>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>0.407</v>
+        <v>0.424</v>
       </c>
       <c r="R13" s="5" t="inlineStr">
         <is>
@@ -4808,7 +4812,7 @@
       </c>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>Matrix table with 2 questions.</t>
+          <t>Matrix table with 3 statements.</t>
         </is>
       </c>
       <c r="T13" s="5" t="inlineStr"/>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.99</v>
+        <v>2.03</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="10">
@@ -902,7 +902,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5.2</v>
+        <v>5.21</v>
       </c>
       <c r="C17" t="inlineStr"/>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="27">
@@ -1012,7 +1012,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.67</v>
+        <v>6.7</v>
       </c>
       <c r="C27" t="inlineStr"/>
     </row>
@@ -1096,7 +1096,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SDE</t>
+          <t xml:space="preserve">  ↳ Substance use</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -1107,23 +1107,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Substance use</t>
+          <t xml:space="preserve">  ↳ Positive mental health</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Positive mental health</t>
+          <t xml:space="preserve">  ↳ SDE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="38">
@@ -1911,151 +1911,169 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="n">
+      <c r="B8" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Nutrition</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>How many servings of fruits and vegetables do you usually have per day? (1 serving is 1 medium piece of fruit, 1 cup raw leafy vegetables, ½ cup fresh/frozen/canned fruits/vegetables, ¾ cup fruit/vegetable juice, or ¼ dried fruit)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>1=0 2=1-2 3=3-4 4=5 or more</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>69.79000000000001</v>
+      </c>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>Clarity, Reading</t>
+        </is>
+      </c>
+      <c r="Q8" s="5" t="n">
+        <v>0.227</v>
+      </c>
+      <c r="R8" s="5" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S8" s="5" t="inlineStr">
+        <is>
+          <t>Definition from American Heart Association 2014</t>
+        </is>
+      </c>
+      <c r="T8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>Concussion / TBI history</t>
         </is>
       </c>
-      <c r="D8" s="6" t="n">
+      <c r="D9" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever knocked out or did you lose consciousness?</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>Mother Question</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>0=No 1=Yes 2=I don’t know 3=Prefer not to say</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0=No 1=Yes 2=I Don't know [mutually exclusive] 3=Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J8" s="6" t="n">
-        <v>77.33</v>
-      </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N8" s="6" t="n">
+      <c r="J9" s="6" t="n">
+        <v>67.77</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
         <is>
           <t>Clarity, Reading</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v>0.212</v>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S8" s="6" t="inlineStr"/>
-      <c r="T8" s="6" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7" t="inlineStr">
-        <is>
-          <t>Concussion / TBI history</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E9" s="7" t="inlineStr">
-        <is>
-          <t>What was the longest time you were knocked out or unconscious? Would you say… (If you aren’t sure, please make your best guess)</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>1=Less than 5 minutes 2=Between 5 and 30 minutes 3=More than 30 minutes but less than 24 hours 4=24 hours or longer 5=I don’t know 6=Prefer not to say</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr"/>
-      <c r="K9" s="7" t="inlineStr"/>
-      <c r="L9" s="7" t="inlineStr"/>
-      <c r="M9" s="7" t="inlineStr"/>
-      <c r="N9" s="7" t="inlineStr"/>
-      <c r="O9" s="7" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr"/>
-      <c r="Q9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="7" t="inlineStr"/>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>Display if “1=Yes” is selected for “Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever knocked out or did you lose consciousness?”</t>
-        </is>
-      </c>
-      <c r="T9" s="7" t="inlineStr">
-        <is>
-          <t>Display if “1=Yes” is selected for “Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever knocked out or did you lose consciousness?”</t>
-        </is>
-      </c>
+      <c r="Q9" s="6" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S9" s="6" t="inlineStr"/>
+      <c r="T9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
@@ -2067,7 +2085,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>How old were you the first time you were knocked out or lost consciousness?</t>
+          <t>What was the longest time you were knocked out or unconscious? Would you say… (If you aren’t sure, please make your best guess)</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -2082,12 +2100,12 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>[open text] force numeric</t>
+          <t>1=Less than 5 minutes 2=Between 5 and 30 minutes 3=More than 30 minutes but less than 24 hours 4=24 hours or longer 5=I Don't know [mutually exclusive] 6=Prefer not to say</t>
         </is>
       </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Categorical (Ordinal)</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr"/>
@@ -2113,224 +2131,206 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
+      <c r="A11" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>Concussion / TBI history</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>How old were you the first time you were knocked out or lost consciousness?</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>[open text] force numeric</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>Numeric</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr"/>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>Display if “1=Yes” is selected for “Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever knocked out or did you lose consciousness?”</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>Display if “1=Yes” is selected for “Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever knocked out or did you lose consciousness?”</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>Concussion / TBI history</t>
         </is>
       </c>
-      <c r="D11" s="6" t="n">
+      <c r="D12" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever dazed or have a gap in your memory from any of the injuries?</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>Mother Question</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>0=No 1=Yes 2=I don’t know 3=Prefer not to say</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>0=No 1=Yes 2=I Don't know [mutually exclusive] 3=Prefer not to say</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="J11" s="6" t="n">
-        <v>75.44</v>
-      </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L11" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M11" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="n">
+      <c r="J12" s="6" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="L12" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>Clarity, Reading</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v>0.216</v>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr"/>
-      <c r="T11" s="6" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="n">
+      <c r="Q12" s="6" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="S12" s="6" t="inlineStr"/>
+      <c r="T12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Concussion / TBI history</t>
         </is>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D13" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>How old were you the first time you were dazed or have a gap in your memory from an injury?</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>Follow-up Question</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G13" s="7" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>[open text] force numeric</t>
         </is>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>Numeric</t>
         </is>
       </c>
-      <c r="J12" s="7" t="inlineStr"/>
-      <c r="K12" s="7" t="inlineStr"/>
-      <c r="L12" s="7" t="inlineStr"/>
-      <c r="M12" s="7" t="inlineStr"/>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr"/>
-      <c r="P12" s="7" t="inlineStr"/>
-      <c r="Q12" s="7" t="n">
+      <c r="J13" s="7" t="inlineStr"/>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>Display if “1=Yes” is selected for “Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever dazed or have a gap in your memory from any of the injuries?” injuries to your head or neck that you have had in your lifetime, were you ever dazed or have a gap in your memory from any of the injuries?”</t>
         </is>
       </c>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="T13" s="7" t="inlineStr">
         <is>
           <t>Display if “1=Yes” is selected for “Thinking about any injuries to your head or neck that you have had in your lifetime, were you ever dazed or have a gap in your memory from any of the injuries?” injuries to your head or neck that you have had in your lifetime, were you ever dazed or have a gap in your memory from any of the injuries?”</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Nutrition</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>How many servings of fruits and vegetables do you usually have per day? (1 serving is 1 medium piece of fruit, 1 cup raw leafy vegetables, ½ cup fresh/frozen/canned fruits/vegetables, ¾ cup fruit/vegetable juice, or ¼ dried fruit)</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>1=0 2=1-2 3=3-4 4=5 or more</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>69.79000000000001</v>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="L13" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="M13" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="O13" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>Clarity, Reading</t>
-        </is>
-      </c>
-      <c r="Q13" s="5" t="n">
-        <v>0.227</v>
-      </c>
-      <c r="R13" s="5" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="S13" s="5" t="inlineStr">
-        <is>
-          <t>Definition from American Heart Association 2014</t>
-        </is>
-      </c>
-      <c r="T13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
@@ -2498,7 +2498,7 @@
       <c r="G16" s="5" t="inlineStr"/>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder  13=Other chronic disease  14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
+          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder  13=Other chronic disease  14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -3894,7 +3894,7 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr">
         <is>
-          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree  6=Don’t know</t>
+          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree  6=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
@@ -3903,7 +3903,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>68.31999999999999</v>
+        <v>59.53</v>
       </c>
       <c r="K2" s="5" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="Q2" s="5" t="n">
-        <v>0.063</v>
+        <v>0.081</v>
       </c>
       <c r="R2" s="5" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>1=0 times 2=1 time 3=2 times 4=3 to 5 times 5=6 to 9 times 6=10 or more times 7=Don’t know</t>
+          <t xml:space="preserve">1=0 times 2=1 time 3=2 times 4=3 to 5 times 5=6 to 9 times 6=10 or more times 7=Don't know [mutually exclusive] </t>
         </is>
       </c>
       <c r="I4" s="7" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>1=No negative experience 2=Harassed/Bullied online 3=Cyber stalking 4=Flaming, whereby someone is being encouraged (egged on) to die by suicide 5=Had someone create/share embarrassing images of you using Ai (e.g., deep fakes) 6=Imposter Scam,for falsely demanding money from family and friends 7=Others</t>
+          <t>1=No negative experience [mutually exclusive] 2=Harassed/Bullied online 3=Cyber stalking 4=Flaming, whereby someone is being encouraged (egged on) to die by suicide 5=Had someone create/share embarrassing images of you using Ai (e.g., deep fakes) 6=Imposter Scam,for falsely demanding money from family and friends 7=Others</t>
         </is>
       </c>
       <c r="I12" s="7" t="inlineStr">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember 8=None of these</t>
+          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -6580,17 +6580,17 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>SDE</t>
+          <t>Positive mental health</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr"/>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>Please answer the following questions as honestly as possible. Do you often feel the desire to eat when you are emotionally upset or stressed? Do you often feel that you can't control what or how much you eat? Do you sometimes make yourself throw up (vomit) to control your weight? Are you often preoccupied with a desire to be thinner? Do you believe yourself to be fat when others say you are thin?</t>
+          <t>Below are 8 statements with which you may agree or disagree. Using the 1-7 scale below, indicate your agreement with each item by indicating that response for each statement. I lead a purposeful and meaningful life. My social relationships are supportive and rewarding. I am engaged and interested in my daily activities. I actively contribute to the happiness and well-being of others. I am competent and capable in the activities that are important to me. I am a good person and live a good life. I am optimistic about my future. People respect me.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
@@ -6601,16 +6601,16 @@
       <c r="G21" s="5" t="inlineStr"/>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>1=Yes 0=No</t>
+          <t>1=Strongly disagree 2=Disagree 3=Slightly disagree 4=Mixed or neither agree nor disagree 5=Slightly agree 6=Agree 7=Strongly agree</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="J21" s="5" t="n">
-        <v>68.06999999999999</v>
+        <v>43.03</v>
       </c>
       <c r="K21" s="5" t="inlineStr">
         <is>
@@ -6624,11 +6624,11 @@
       </c>
       <c r="M21" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
@@ -6637,11 +6637,11 @@
       </c>
       <c r="P21" s="5" t="inlineStr">
         <is>
-          <t>Assumptions, Clarity, Reading, Sensitivity/Bias</t>
+          <t>Clarity, Reading, Response Categories</t>
         </is>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>0.397</v>
+        <v>0.414</v>
       </c>
       <c r="R21" s="5" t="inlineStr">
         <is>
@@ -6650,31 +6650,27 @@
       </c>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>Included if ‘Eating and Body Image’ module not selected SDE (Maguen et al., 2018)</t>
-        </is>
-      </c>
-      <c r="T21" s="5" t="inlineStr">
-        <is>
-          <t>Included if ‘Eating and Body Image’ module not selected SDE (Maguen et al., 2018)</t>
-        </is>
-      </c>
+          <t>Matrix table with 8 statements. Flourishing Scale (Diener &amp; Biswas-Diener, 2009)</t>
+        </is>
+      </c>
+      <c r="T21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>Positive mental health</t>
+          <t>Suicidality</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr"/>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>Below are 8 statements with which you may agree or disagree. Using the 1-7 scale below, indicate your agreement with each item by indicating that response for each statement. I lead a purposeful and meaningful life. My social relationships are supportive and rewarding. I am engaged and interested in my daily activities. I actively contribute to the happiness and well-being of others. I am competent and capable in the activities that are important to me. I am a good person and live a good life. I am optimistic about my future. People respect me.</t>
+          <t>In the past year, did you… … make a plan for attempting suicide? … attempt suicide?</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -6685,7 +6681,7 @@
       <c r="G22" s="5" t="inlineStr"/>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>1=Strongly disagree 2=Disagree 3=Slightly disagree 4=Mixed or neither agree nor disagree 5=Slightly agree 6=Agree 7=Strongly agree</t>
+          <t>1=Yes 0=No</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -6694,11 +6690,11 @@
         </is>
       </c>
       <c r="J22" s="5" t="n">
-        <v>43.03</v>
+        <v>75.88</v>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="L22" s="5" t="inlineStr">
@@ -6716,16 +6712,16 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="P22" s="5" t="inlineStr">
         <is>
-          <t>Clarity, Reading, Response Categories</t>
+          <t>Knowledge/Memory, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q22" s="5" t="n">
-        <v>0.414</v>
+        <v>0.415</v>
       </c>
       <c r="R22" s="5" t="inlineStr">
         <is>
@@ -6734,7 +6730,7 @@
       </c>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>Matrix table with 8 statements. Flourishing Scale (Diener &amp; Biswas-Diener, 2009)</t>
+          <t>Matrix table with 2 questions.</t>
         </is>
       </c>
       <c r="T22" s="5" t="inlineStr"/>
@@ -6744,17 +6740,17 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>Suicidality</t>
+          <t>SDE</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>In the past year, did you… … make a plan for attempting suicide? … attempt suicide?</t>
+          <t>Please answer the following questions as honestly as possible. 1. Do you often feel the desire to eat when you are emotionally upset or stressed? 2. Do you often feel that you can't control what or how much you eat? 3. Do you sometimes make yourself throw up (vomit) to control your weight? 4. Are you often preoccupied with a desire to be thinner? 5. Do you believe yourself to be fat when others say you are thin?</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -6774,7 +6770,7 @@
         </is>
       </c>
       <c r="J23" s="5" t="n">
-        <v>75.88</v>
+        <v>74.13</v>
       </c>
       <c r="K23" s="5" t="inlineStr">
         <is>
@@ -6796,16 +6792,16 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="P23" s="5" t="inlineStr">
         <is>
-          <t>Knowledge/Memory, Sensitivity/Bias</t>
+          <t>Assumptions, Clarity, Reading, Sensitivity/Bias</t>
         </is>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>0.415</v>
+        <v>0.435</v>
       </c>
       <c r="R23" s="5" t="inlineStr">
         <is>
@@ -6814,7 +6810,7 @@
       </c>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>Matrix table with 2 questions.</t>
+          <t xml:space="preserve">Matrix </t>
         </is>
       </c>
       <c r="T23" s="5" t="inlineStr"/>
@@ -8371,7 +8367,7 @@
       <c r="G15" s="6" t="inlineStr"/>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
@@ -8380,7 +8376,7 @@
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
@@ -8411,11 +8407,11 @@
         </is>
       </c>
       <c r="Q15" s="6" t="n">
-        <v>0.597</v>
+        <v>0.6</v>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="S15" s="6" t="inlineStr"/>
@@ -8577,7 +8573,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
+          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
@@ -8639,7 +8635,7 @@
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor  4=Took the medication(s) without a prescription 5=Don’t know</t>
+          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor  4=Took the medication(s) without a prescription 5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I19" s="7" t="inlineStr">
@@ -8701,7 +8697,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -9058,7 +9054,7 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>Which of the following are important reasons why you received the counselling services? (Select all that apply)</t>
+          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -9431,7 +9427,7 @@
       <c r="G31" s="6" t="inlineStr"/>
       <c r="H31" s="6" t="inlineStr">
         <is>
-          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
+          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don't know [mutually exclusive] 13=Other mental health condition (please specify)</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
@@ -9513,7 +9509,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Others  5=Don’t know</t>
+          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I32" s="7" t="inlineStr">
@@ -9575,7 +9571,7 @@
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Others  5=Don’t know</t>
+          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I33" s="7" t="inlineStr">
@@ -9637,7 +9633,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Others  7=Don’t know</t>
+          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Others  7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I34" s="7" t="inlineStr">
@@ -9699,7 +9695,7 @@
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Others 7=Don’t know</t>
+          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Others 7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I35" s="7" t="inlineStr">
@@ -9761,7 +9757,7 @@
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Others  5=Don’t know</t>
+          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I36" s="7" t="inlineStr">
@@ -9823,7 +9819,7 @@
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Others  5=Don’t know</t>
+          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I37" s="7" t="inlineStr">
@@ -9885,7 +9881,7 @@
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Others 7=Don’t know</t>
+          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Others 7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I38" s="7" t="inlineStr">
@@ -9947,7 +9943,7 @@
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Others  7=Don’t know</t>
+          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Others  7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I39" s="7" t="inlineStr">
@@ -10009,7 +10005,7 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Others 12=Don’t know</t>
+          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Others 12=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I40" s="7" t="inlineStr">
@@ -10071,7 +10067,7 @@
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Others  3=Don’t know</t>
+          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Others  3=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="I41" s="7" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -8170,7 +8170,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
+          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my beliefs (e.g., faith, gender, etc.)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -9069,7 +9069,7 @@
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Others</t>
+          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help  10= A health professional recommended or referred me to seek help. 12=Others</t>
         </is>
       </c>
       <c r="I26" s="7" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -5998,7 +5998,7 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>We know that there are many experiences in the online space, ranging from positive to neutral to negative. For this item, we want to know more about your negative online experiences. Please select all the negative experiences you have had in online spaces (such as social media) in the past year.</t>
+          <t>We know that there are many experiences in the online space, ranging from positive to neutral to negative. For this item, we want to know more about your negative online experiences. Please select all the negative experiences you have had in online spaces (such as social media) in the past year. (Select all that apply)</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -6750,7 +6750,12 @@
       <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Please answer the following questions as honestly as possible. 1. Do you often feel the desire to eat when you are emotionally upset or stressed? 2. Do you often feel that you can't control what or how much you eat? 3. Do you sometimes make yourself throw up (vomit) to control your weight? 4. Are you often preoccupied with a desire to be thinner? 5. Do you believe yourself to be fat when others say you are thin?</t>
+          <t>Please answer the following questions as honestly as possible.
+1. Do you often feel the desire to eat when you are emotionally upset or stressed?
+2. Do you often feel that you can't control what or how much you eat?
+3. Do you sometimes make yourself throw up (vomit) to control your weight?
+4. Are you often preoccupied with a desire to be thinner?
+5. Do you believe yourself to be fat when others say you are thin?</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -6998,7 +6998,7 @@
       <c r="G26" s="5" t="inlineStr"/>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>1=Cut myself 2=Burned myself 3=Punched or banged myself 4=Scratched myself 5=Pulled my hair 6=Bit myself 7=Interfered with wound healing 8=Carved words or symbols into skin 9=Rubbed sharp objects into skin 10=Punched or banged an object to hurt myself 11=Other (please specify) 12=No, none of these [mutually exclusive]</t>
+          <t>1=Cut myself 2=Burned myself 3=Punched or banged myself 4=Scratched myself 5=Pulled my hair 6=Bit myself 7=Interfered with wound healing 8=Carved words or symbols into skin 9=Rubbed sharp objects into skin 10=Punched or banged an object to hurt myself 11=Others 12=No, none of these [mutually exclusive]</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
@@ -7007,7 +7007,7 @@
         </is>
       </c>
       <c r="J26" s="5" t="n">
-        <v>59.75</v>
+        <v>61.88</v>
       </c>
       <c r="K26" s="5" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         </is>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>0.481</v>
+        <v>0.476</v>
       </c>
       <c r="R26" s="5" t="inlineStr">
         <is>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -711,7 +711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1019,62 +1019,62 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Eating and body image</t>
+          <t xml:space="preserve">  ↳ Psychosis Screen</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="n">
-        <v>0.09</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Psychosis Screen</t>
+          <t xml:space="preserve">  ↳ Loneliness</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Loneliness</t>
+          <t xml:space="preserve">  ↳ Social media/internet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Social media/internet</t>
+          <t xml:space="preserve">  ↳ Sleep</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="n">
-        <v>0.32</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Sleep</t>
+          <t xml:space="preserve">  ↳ Anxiety (GAD-7)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Anxiety (GAD-7)</t>
+          <t xml:space="preserve">  ↳ Suicide Contagion</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -1085,139 +1085,139 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Suicide Contagion</t>
+          <t xml:space="preserve">  ↳ Substance use</t>
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Substance use</t>
+          <t xml:space="preserve">  ↳ Positive mental health</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Positive mental health</t>
+          <t xml:space="preserve">  ↳ Academic Impairment</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.41</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ SDE</t>
+          <t xml:space="preserve">  ↳ Non-suicidal self-injury</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Academic Impairment</t>
+          <t xml:space="preserve">  ↳ Exercise</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Non-suicidal self-injury</t>
+          <t xml:space="preserve">  ↳ Eating and body image</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="n">
-        <v>0.48</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Exercise</t>
+          <t xml:space="preserve">  ↳ Suicidality</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="n">
-        <v>0.52</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Suicidality</t>
+          <t xml:space="preserve">  ↳ Depression (PHQ-9)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="n">
-        <v>0.88</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Depression (PHQ-9)</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="n">
-        <v>1.1</v>
-      </c>
+          <t>Mental Health Service Utilizati</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>6.72</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mental Health Service Utilizati</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>6.72</v>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Satisfaction with counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Insurance</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Insurance</t>
+          <t xml:space="preserve">  ↳ Disability</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Disability</t>
+          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -1228,99 +1228,88 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of counseling/therapy</t>
+          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Knowledge of campus services</t>
+          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Help-seeking intentions</t>
+          <t xml:space="preserve">  ↳ Diagnosed mental illnesses</t>
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="n">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Diagnosed mental illnesses</t>
+          <t xml:space="preserve">  ↳ Use of medication</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="n">
-        <v>0.52</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Use of medication</t>
+          <t xml:space="preserve">  ↳ Stigma</t>
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Stigma</t>
+          <t xml:space="preserve">  ↳ Perceived need</t>
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="n">
-        <v>0.62</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Perceived need</t>
+          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.66</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">  ↳ Barriers to help-seeking</t>
+          <t xml:space="preserve">  ↳ Informal help-seeking</t>
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  ↳ Informal help-seeking</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="n">
         <v>1.65</v>
       </c>
     </row>
@@ -6744,7 +6733,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>SDE</t>
+          <t>Eating and body image</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr"/>

--- a/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score_reordered.xlsx
@@ -6410,7 +6410,7 @@
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these</t>
+          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these [mutually exclusive]</t>
         </is>
       </c>
       <c r="I18" s="7" t="inlineStr">
